--- a/results/per_capita_hours/per_capita_hours_summary.xlsx
+++ b/results/per_capita_hours/per_capita_hours_summary.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="38">
   <si>
     <t>策略</t>
   </si>
@@ -25,6 +25,9 @@
     <t>城市拼音</t>
   </si>
   <si>
+    <t>城市标签</t>
+  </si>
+  <si>
     <t>情景</t>
   </si>
   <si>
@@ -37,9 +40,6 @@
     <t>Hours_Per_Resident</t>
   </si>
   <si>
-    <t>城市标签</t>
-  </si>
-  <si>
     <t>现状</t>
   </si>
   <si>
@@ -49,6 +49,12 @@
     <t>定容</t>
   </si>
   <si>
+    <t>扩容_26C</t>
+  </si>
+  <si>
+    <t>定容_26C</t>
+  </si>
+  <si>
     <t>北京市</t>
   </si>
   <si>
@@ -85,6 +91,24 @@
     <t>xia4men2shi4</t>
   </si>
   <si>
+    <t>Bei3jing1s</t>
+  </si>
+  <si>
+    <t>Shang4hai3s</t>
+  </si>
+  <si>
+    <t>Guang3zhou1s</t>
+  </si>
+  <si>
+    <t>Shen1zhen4s</t>
+  </si>
+  <si>
+    <t>Wu3han4s</t>
+  </si>
+  <si>
+    <t>Xia4men2s</t>
+  </si>
+  <si>
     <t>2020 Baseline</t>
   </si>
   <si>
@@ -104,24 +128,6 @@
   </si>
   <si>
     <t>2060 RCP 8.5</t>
-  </si>
-  <si>
-    <t>Bei3jing1s</t>
-  </si>
-  <si>
-    <t>Shang4hai3s</t>
-  </si>
-  <si>
-    <t>Guang3zhou1s</t>
-  </si>
-  <si>
-    <t>Shen1zhen4s</t>
-  </si>
-  <si>
-    <t>Wu3han4s</t>
-  </si>
-  <si>
-    <t>Xia4men2s</t>
   </si>
 </sst>
 </file>
@@ -479,7 +485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H79"/>
+  <dimension ref="A1:H115"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -513,25 +519,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2">
+        <v>25</v>
+      </c>
+      <c r="E2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2">
         <v>6084353.362053598</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>5900281.724590417</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>1.031197092961855</v>
-      </c>
-      <c r="H2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -539,25 +545,25 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3">
         <v>11503824.4077344</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>5900281.724590418</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>1.949707648668754</v>
-      </c>
-      <c r="H3" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -565,25 +571,25 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D4" t="s">
         <v>25</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4">
         <v>16088522.54070038</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>5900281.724590417</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>2.726738025685918</v>
-      </c>
-      <c r="H4" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -591,25 +597,25 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5">
         <v>26019349.75405014</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>5900281.724590417</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>4.409848710377696</v>
-      </c>
-      <c r="H5" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -617,25 +623,25 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6">
         <v>36290181.92474034</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>5900281.724590417</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>6.150584602341089</v>
-      </c>
-      <c r="H6" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -643,25 +649,25 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7">
+        <v>25</v>
+      </c>
+      <c r="E7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7">
         <v>40289854.07210815</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>5900281.724590417</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>6.828462767157948</v>
-      </c>
-      <c r="H7" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -669,25 +675,25 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8">
-        <v>92927897.47736897</v>
+        <v>25</v>
+      </c>
+      <c r="E8" t="s">
+        <v>37</v>
       </c>
       <c r="F8">
+        <v>92927897.47736895</v>
+      </c>
+      <c r="G8">
         <v>5900281.724590417</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>15.74973904891292</v>
-      </c>
-      <c r="H8" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -695,25 +701,25 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9">
+        <v>25</v>
+      </c>
+      <c r="E9" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9">
         <v>12105154.88352069</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>5900281.724590417</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>2.05162320183296</v>
-      </c>
-      <c r="H9" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -721,25 +727,25 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D10" t="s">
         <v>25</v>
       </c>
-      <c r="E10">
+      <c r="E10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10">
         <v>21292652.95341992</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>5900281.724590417</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>3.608751911739944</v>
-      </c>
-      <c r="H10" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -747,25 +753,25 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D11" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11">
+        <v>25</v>
+      </c>
+      <c r="E11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11">
         <v>27655595.63203176</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>5900281.724590417</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>4.687165278358221</v>
-      </c>
-      <c r="H11" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -773,25 +779,25 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D12" t="s">
-        <v>27</v>
-      </c>
-      <c r="E12">
+        <v>25</v>
+      </c>
+      <c r="E12" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12">
         <v>49072616.18256301</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>5900281.724590418</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>8.316995437361003</v>
-      </c>
-      <c r="H12" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -799,25 +805,25 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D13" t="s">
-        <v>28</v>
-      </c>
-      <c r="E13">
+        <v>25</v>
+      </c>
+      <c r="E13" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13">
         <v>45499452.97391333</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>5900281.724590417</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>7.711403471513352</v>
-      </c>
-      <c r="H13" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -825,25 +831,25 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D14" t="s">
-        <v>29</v>
-      </c>
-      <c r="E14">
+        <v>25</v>
+      </c>
+      <c r="E14" t="s">
+        <v>37</v>
+      </c>
+      <c r="F14">
         <v>155793777.8074042</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>5900281.724590417</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>26.40446424076792</v>
-      </c>
-      <c r="H14" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -851,25 +857,25 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15">
+        <v>26</v>
+      </c>
+      <c r="E15" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15">
         <v>47310862.42603313</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <v>4875767.960493487</v>
       </c>
-      <c r="G15">
-        <v>9.703263733913351</v>
-      </c>
-      <c r="H15" t="s">
-        <v>31</v>
+      <c r="H15">
+        <v>9.703263733913353</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -877,25 +883,25 @@
         <v>9</v>
       </c>
       <c r="B16" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D16" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16">
+        <v>26</v>
+      </c>
+      <c r="E16" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16">
         <v>249832938.8970911</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>4875767.960493487</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>51.23971052794009</v>
-      </c>
-      <c r="H16" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -903,25 +909,25 @@
         <v>9</v>
       </c>
       <c r="B17" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D17" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17">
+        <v>26</v>
+      </c>
+      <c r="E17" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17">
         <v>124164578.7435003</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>4875767.960493487</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>25.46564556590042</v>
-      </c>
-      <c r="H17" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -929,25 +935,25 @@
         <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C18" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D18" t="s">
         <v>26</v>
       </c>
-      <c r="E18">
+      <c r="E18" t="s">
+        <v>34</v>
+      </c>
+      <c r="F18">
         <v>166114106.8393903</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <v>4875767.960493487</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>34.06932163001816</v>
-      </c>
-      <c r="H18" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -955,25 +961,25 @@
         <v>9</v>
       </c>
       <c r="B19" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C19" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D19" t="s">
-        <v>27</v>
-      </c>
-      <c r="E19">
+        <v>26</v>
+      </c>
+      <c r="E19" t="s">
+        <v>35</v>
+      </c>
+      <c r="F19">
         <v>297684815.1021526</v>
       </c>
-      <c r="F19">
+      <c r="G19">
         <v>4875767.960493487</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <v>61.05393396777301</v>
-      </c>
-      <c r="H19" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -981,25 +987,25 @@
         <v>9</v>
       </c>
       <c r="B20" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C20" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D20" t="s">
-        <v>28</v>
-      </c>
-      <c r="E20">
+        <v>26</v>
+      </c>
+      <c r="E20" t="s">
+        <v>36</v>
+      </c>
+      <c r="F20">
         <v>336275644.4580898</v>
       </c>
-      <c r="F20">
+      <c r="G20">
         <v>4875767.960493487</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>68.96875470342411</v>
-      </c>
-      <c r="H20" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1007,25 +1013,25 @@
         <v>9</v>
       </c>
       <c r="B21" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C21" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D21" t="s">
-        <v>29</v>
-      </c>
-      <c r="E21">
+        <v>26</v>
+      </c>
+      <c r="E21" t="s">
+        <v>37</v>
+      </c>
+      <c r="F21">
         <v>548319631.2929255</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>4875767.960493487</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>112.458106237982</v>
-      </c>
-      <c r="H21" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1033,25 +1039,25 @@
         <v>10</v>
       </c>
       <c r="B22" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C22" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D22" t="s">
-        <v>24</v>
-      </c>
-      <c r="E22">
+        <v>26</v>
+      </c>
+      <c r="E22" t="s">
+        <v>32</v>
+      </c>
+      <c r="F22">
         <v>282264703.3045797</v>
       </c>
-      <c r="F22">
+      <c r="G22">
         <v>4875767.960493487</v>
       </c>
-      <c r="G22">
+      <c r="H22">
         <v>57.89133231762962</v>
-      </c>
-      <c r="H22" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1059,25 +1065,25 @@
         <v>10</v>
       </c>
       <c r="B23" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C23" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D23" t="s">
-        <v>25</v>
-      </c>
-      <c r="E23">
+        <v>26</v>
+      </c>
+      <c r="E23" t="s">
+        <v>33</v>
+      </c>
+      <c r="F23">
         <v>130465411.2634157</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>4875767.960493487</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>26.75792045899801</v>
-      </c>
-      <c r="H23" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1085,25 +1091,25 @@
         <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C24" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D24" t="s">
         <v>26</v>
       </c>
-      <c r="E24">
+      <c r="E24" t="s">
+        <v>34</v>
+      </c>
+      <c r="F24">
         <v>178571061.5903344</v>
       </c>
-      <c r="F24">
+      <c r="G24">
         <v>4875767.960493487</v>
       </c>
-      <c r="G24">
+      <c r="H24">
         <v>36.62419192981054</v>
-      </c>
-      <c r="H24" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1111,25 +1117,25 @@
         <v>10</v>
       </c>
       <c r="B25" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C25" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E25">
+        <v>26</v>
+      </c>
+      <c r="E25" t="s">
+        <v>35</v>
+      </c>
+      <c r="F25">
         <v>368023062.0423386</v>
       </c>
-      <c r="F25">
+      <c r="G25">
         <v>4875767.960493487</v>
       </c>
-      <c r="G25">
+      <c r="H25">
         <v>75.48001976802239</v>
-      </c>
-      <c r="H25" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1137,25 +1143,25 @@
         <v>10</v>
       </c>
       <c r="B26" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C26" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D26" t="s">
-        <v>28</v>
-      </c>
-      <c r="E26">
+        <v>26</v>
+      </c>
+      <c r="E26" t="s">
+        <v>36</v>
+      </c>
+      <c r="F26">
         <v>436178785.8196998</v>
       </c>
-      <c r="F26">
+      <c r="G26">
         <v>4875767.960493487</v>
       </c>
-      <c r="G26">
+      <c r="H26">
         <v>89.45847902400038</v>
-      </c>
-      <c r="H26" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1163,389 +1169,389 @@
         <v>10</v>
       </c>
       <c r="B27" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C27" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D27" t="s">
-        <v>29</v>
-      </c>
-      <c r="E27">
+        <v>26</v>
+      </c>
+      <c r="E27" t="s">
+        <v>37</v>
+      </c>
+      <c r="F27">
         <v>698710388.1267633</v>
       </c>
-      <c r="F27">
+      <c r="G27">
         <v>4875767.960493487</v>
       </c>
-      <c r="G27">
+      <c r="H27">
         <v>143.3026333057993</v>
-      </c>
-      <c r="H27" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C28" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D28" t="s">
-        <v>23</v>
-      </c>
-      <c r="E28">
-        <v>25047504.80641522</v>
+        <v>26</v>
+      </c>
+      <c r="E28" t="s">
+        <v>32</v>
       </c>
       <c r="F28">
-        <v>1488498.682202912</v>
+        <v>23345430.00312043</v>
       </c>
       <c r="G28">
-        <v>16.82736108932662</v>
-      </c>
-      <c r="H28" t="s">
-        <v>32</v>
+        <v>4875767.960493487</v>
+      </c>
+      <c r="H28">
+        <v>4.788051890959467</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C29" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D29" t="s">
-        <v>24</v>
-      </c>
-      <c r="E29">
-        <v>74034829.4328794</v>
+        <v>26</v>
+      </c>
+      <c r="E29" t="s">
+        <v>33</v>
       </c>
       <c r="F29">
-        <v>1488498.682202912</v>
+        <v>7915098.399554222</v>
       </c>
       <c r="G29">
-        <v>49.73792071035707</v>
-      </c>
-      <c r="H29" t="s">
-        <v>32</v>
+        <v>4875767.960493487</v>
+      </c>
+      <c r="H29">
+        <v>1.623354200545901</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C30" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D30" t="s">
-        <v>25</v>
-      </c>
-      <c r="E30">
-        <v>54358480.9799815</v>
+        <v>26</v>
+      </c>
+      <c r="E30" t="s">
+        <v>34</v>
       </c>
       <c r="F30">
-        <v>1488498.682202912</v>
+        <v>11495400.35526426</v>
       </c>
       <c r="G30">
-        <v>36.51899839073648</v>
-      </c>
-      <c r="H30" t="s">
-        <v>32</v>
+        <v>4875767.960493487</v>
+      </c>
+      <c r="H30">
+        <v>2.357659439170848</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C31" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D31" t="s">
         <v>26</v>
       </c>
-      <c r="E31">
-        <v>59508823.20942345</v>
+      <c r="E31" t="s">
+        <v>35</v>
       </c>
       <c r="F31">
-        <v>1488498.682202912</v>
+        <v>20092878.12114714</v>
       </c>
       <c r="G31">
-        <v>39.97909028804315</v>
-      </c>
-      <c r="H31" t="s">
-        <v>32</v>
+        <v>4875767.960493487</v>
+      </c>
+      <c r="H31">
+        <v>4.120966847469398</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C32" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D32" t="s">
-        <v>27</v>
-      </c>
-      <c r="E32">
-        <v>78972639.79064965</v>
+        <v>26</v>
+      </c>
+      <c r="E32" t="s">
+        <v>36</v>
       </c>
       <c r="F32">
-        <v>1488498.682202912</v>
+        <v>24361804.36527121</v>
       </c>
       <c r="G32">
-        <v>53.05522990035415</v>
-      </c>
-      <c r="H32" t="s">
-        <v>32</v>
+        <v>4875767.960493487</v>
+      </c>
+      <c r="H32">
+        <v>4.996506101739405</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C33" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D33" t="s">
-        <v>28</v>
-      </c>
-      <c r="E33">
-        <v>92542070.43296188</v>
+        <v>26</v>
+      </c>
+      <c r="E33" t="s">
+        <v>37</v>
       </c>
       <c r="F33">
-        <v>1488498.682202912</v>
+        <v>53401501.13574702</v>
       </c>
       <c r="G33">
-        <v>62.17141576235979</v>
-      </c>
-      <c r="H33" t="s">
-        <v>32</v>
+        <v>4875767.960493487</v>
+      </c>
+      <c r="H33">
+        <v>10.95242873911131</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B34" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C34" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D34" t="s">
-        <v>29</v>
-      </c>
-      <c r="E34">
-        <v>98942739.24104676</v>
+        <v>26</v>
+      </c>
+      <c r="E34" t="s">
+        <v>32</v>
       </c>
       <c r="F34">
-        <v>1488498.682202912</v>
+        <v>40309054.98713735</v>
       </c>
       <c r="G34">
-        <v>66.47149938662756</v>
-      </c>
-      <c r="H34" t="s">
-        <v>32</v>
+        <v>4875767.960493487</v>
+      </c>
+      <c r="H34">
+        <v>8.267221761524841</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B35" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C35" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D35" t="s">
-        <v>24</v>
-      </c>
-      <c r="E35">
-        <v>80041703.25937352</v>
+        <v>26</v>
+      </c>
+      <c r="E35" t="s">
+        <v>33</v>
       </c>
       <c r="F35">
-        <v>1488498.682202912</v>
+        <v>8671326.41632206</v>
       </c>
       <c r="G35">
-        <v>53.77344583262605</v>
-      </c>
-      <c r="H35" t="s">
-        <v>32</v>
+        <v>4875767.960493487</v>
+      </c>
+      <c r="H35">
+        <v>1.778453463450795</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B36" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C36" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D36" t="s">
-        <v>25</v>
-      </c>
-      <c r="E36">
-        <v>59195277.33716299</v>
+        <v>26</v>
+      </c>
+      <c r="E36" t="s">
+        <v>34</v>
       </c>
       <c r="F36">
-        <v>1488498.682202912</v>
+        <v>11013934.35343651</v>
       </c>
       <c r="G36">
-        <v>39.76844457097982</v>
-      </c>
-      <c r="H36" t="s">
-        <v>32</v>
+        <v>4875767.960493487</v>
+      </c>
+      <c r="H36">
+        <v>2.258912737988821</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B37" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C37" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D37" t="s">
         <v>26</v>
       </c>
-      <c r="E37">
-        <v>62335381.75197408</v>
+      <c r="E37" t="s">
+        <v>35</v>
       </c>
       <c r="F37">
-        <v>1488498.682202912</v>
+        <v>29679366.18381804</v>
       </c>
       <c r="G37">
-        <v>41.87802280061176</v>
-      </c>
-      <c r="H37" t="s">
-        <v>32</v>
+        <v>4875767.960493487</v>
+      </c>
+      <c r="H37">
+        <v>6.087116209035945</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B38" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C38" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D38" t="s">
-        <v>27</v>
-      </c>
-      <c r="E38">
-        <v>83142580.03190084</v>
+        <v>26</v>
+      </c>
+      <c r="E38" t="s">
+        <v>36</v>
       </c>
       <c r="F38">
-        <v>1488498.682202912</v>
+        <v>36406925.52336985</v>
       </c>
       <c r="G38">
-        <v>55.85667023154736</v>
-      </c>
-      <c r="H38" t="s">
-        <v>32</v>
+        <v>4875767.960493487</v>
+      </c>
+      <c r="H38">
+        <v>7.466911021681398</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B39" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D39" t="s">
-        <v>28</v>
-      </c>
-      <c r="E39">
-        <v>101551618.3547024</v>
+        <v>26</v>
+      </c>
+      <c r="E39" t="s">
+        <v>37</v>
       </c>
       <c r="F39">
-        <v>1488498.682202912</v>
+        <v>115498270.7454035</v>
       </c>
       <c r="G39">
-        <v>68.22419097100614</v>
-      </c>
-      <c r="H39" t="s">
-        <v>32</v>
+        <v>4875767.960493487</v>
+      </c>
+      <c r="H39">
+        <v>23.68822135943353</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B40" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C40" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D40" t="s">
-        <v>29</v>
-      </c>
-      <c r="E40">
-        <v>119846953.147862</v>
+        <v>27</v>
+      </c>
+      <c r="E40" t="s">
+        <v>31</v>
       </c>
       <c r="F40">
-        <v>1488498.682202912</v>
+        <v>25047504.80641522</v>
       </c>
       <c r="G40">
-        <v>80.51532364845217</v>
-      </c>
-      <c r="H40" t="s">
-        <v>32</v>
+        <v>1488498.682202911</v>
+      </c>
+      <c r="H40">
+        <v>16.82736108932662</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B41" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D41" t="s">
-        <v>23</v>
-      </c>
-      <c r="E41">
-        <v>107009531.6959314</v>
+        <v>27</v>
+      </c>
+      <c r="E41" t="s">
+        <v>32</v>
       </c>
       <c r="F41">
-        <v>3237432.425417896</v>
+        <v>74034829.4328794</v>
       </c>
       <c r="G41">
-        <v>33.05382711798789</v>
-      </c>
-      <c r="H41" t="s">
-        <v>33</v>
+        <v>1488498.682202911</v>
+      </c>
+      <c r="H41">
+        <v>49.73792071035707</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1553,25 +1559,25 @@
         <v>9</v>
       </c>
       <c r="B42" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C42" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D42" t="s">
-        <v>24</v>
-      </c>
-      <c r="E42">
-        <v>201944877.8190013</v>
+        <v>27</v>
+      </c>
+      <c r="E42" t="s">
+        <v>33</v>
       </c>
       <c r="F42">
-        <v>3237432.425417896</v>
+        <v>54358480.9799815</v>
       </c>
       <c r="G42">
-        <v>62.3780982217517</v>
-      </c>
-      <c r="H42" t="s">
-        <v>33</v>
+        <v>1488498.682202911</v>
+      </c>
+      <c r="H42">
+        <v>36.51899839073648</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1579,25 +1585,25 @@
         <v>9</v>
       </c>
       <c r="B43" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C43" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D43" t="s">
-        <v>25</v>
-      </c>
-      <c r="E43">
-        <v>201512199.3455853</v>
+        <v>27</v>
+      </c>
+      <c r="E43" t="s">
+        <v>34</v>
       </c>
       <c r="F43">
-        <v>3237432.425417896</v>
+        <v>59508823.20942345</v>
       </c>
       <c r="G43">
-        <v>62.24444957166129</v>
-      </c>
-      <c r="H43" t="s">
-        <v>33</v>
+        <v>1488498.682202911</v>
+      </c>
+      <c r="H43">
+        <v>39.97909028804315</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -1605,25 +1611,25 @@
         <v>9</v>
       </c>
       <c r="B44" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C44" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D44" t="s">
-        <v>26</v>
-      </c>
-      <c r="E44">
-        <v>283203798.3112867</v>
+        <v>27</v>
+      </c>
+      <c r="E44" t="s">
+        <v>35</v>
       </c>
       <c r="F44">
-        <v>3237432.425417896</v>
+        <v>78972639.79064965</v>
       </c>
       <c r="G44">
-        <v>87.47790257729626</v>
-      </c>
-      <c r="H44" t="s">
-        <v>33</v>
+        <v>1488498.682202911</v>
+      </c>
+      <c r="H44">
+        <v>53.05522990035415</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -1631,25 +1637,25 @@
         <v>9</v>
       </c>
       <c r="B45" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C45" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D45" t="s">
         <v>27</v>
       </c>
-      <c r="E45">
-        <v>288357254.3810459</v>
+      <c r="E45" t="s">
+        <v>36</v>
       </c>
       <c r="F45">
-        <v>3237432.425417896</v>
+        <v>92542070.43296187</v>
       </c>
       <c r="G45">
-        <v>89.0697369054194</v>
-      </c>
-      <c r="H45" t="s">
-        <v>33</v>
+        <v>1488498.682202911</v>
+      </c>
+      <c r="H45">
+        <v>62.17141576235979</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -1657,51 +1663,51 @@
         <v>9</v>
       </c>
       <c r="B46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C46" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D46" t="s">
-        <v>28</v>
-      </c>
-      <c r="E46">
-        <v>274266005.9898455</v>
+        <v>27</v>
+      </c>
+      <c r="E46" t="s">
+        <v>37</v>
       </c>
       <c r="F46">
-        <v>3237432.425417896</v>
+        <v>98942739.24104676</v>
       </c>
       <c r="G46">
-        <v>84.71713690037639</v>
-      </c>
-      <c r="H46" t="s">
-        <v>33</v>
+        <v>1488498.682202911</v>
+      </c>
+      <c r="H46">
+        <v>66.47149938662756</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B47" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C47" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D47" t="s">
-        <v>29</v>
-      </c>
-      <c r="E47">
-        <v>462637564.4554803</v>
+        <v>27</v>
+      </c>
+      <c r="E47" t="s">
+        <v>32</v>
       </c>
       <c r="F47">
-        <v>3237432.425417896</v>
+        <v>80041703.25937352</v>
       </c>
       <c r="G47">
-        <v>142.9026165374747</v>
-      </c>
-      <c r="H47" t="s">
-        <v>33</v>
+        <v>1488498.682202911</v>
+      </c>
+      <c r="H47">
+        <v>53.77344583262605</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -1709,25 +1715,25 @@
         <v>10</v>
       </c>
       <c r="B48" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C48" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D48" t="s">
-        <v>24</v>
-      </c>
-      <c r="E48">
-        <v>203565326.0998279</v>
+        <v>27</v>
+      </c>
+      <c r="E48" t="s">
+        <v>33</v>
       </c>
       <c r="F48">
-        <v>3237432.425417896</v>
+        <v>59195277.33716299</v>
       </c>
       <c r="G48">
-        <v>62.8786332346539</v>
-      </c>
-      <c r="H48" t="s">
-        <v>33</v>
+        <v>1488498.682202911</v>
+      </c>
+      <c r="H48">
+        <v>39.76844457097982</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -1735,25 +1741,25 @@
         <v>10</v>
       </c>
       <c r="B49" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C49" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D49" t="s">
-        <v>25</v>
-      </c>
-      <c r="E49">
-        <v>206718927.1378156</v>
+        <v>27</v>
+      </c>
+      <c r="E49" t="s">
+        <v>34</v>
       </c>
       <c r="F49">
-        <v>3237432.425417896</v>
+        <v>62335381.75197408</v>
       </c>
       <c r="G49">
-        <v>63.8527388293307</v>
-      </c>
-      <c r="H49" t="s">
-        <v>33</v>
+        <v>1488498.682202911</v>
+      </c>
+      <c r="H49">
+        <v>41.87802280061176</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -1761,25 +1767,25 @@
         <v>10</v>
       </c>
       <c r="B50" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C50" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D50" t="s">
-        <v>26</v>
-      </c>
-      <c r="E50">
-        <v>259568173.3052293</v>
+        <v>27</v>
+      </c>
+      <c r="E50" t="s">
+        <v>35</v>
       </c>
       <c r="F50">
-        <v>3237432.425417896</v>
+        <v>83142580.03190084</v>
       </c>
       <c r="G50">
-        <v>80.17717104063526</v>
-      </c>
-      <c r="H50" t="s">
-        <v>33</v>
+        <v>1488498.682202911</v>
+      </c>
+      <c r="H50">
+        <v>55.85667023154736</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -1787,25 +1793,25 @@
         <v>10</v>
       </c>
       <c r="B51" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C51" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D51" t="s">
         <v>27</v>
       </c>
-      <c r="E51">
-        <v>298585365.3274482</v>
+      <c r="E51" t="s">
+        <v>36</v>
       </c>
       <c r="F51">
-        <v>3237432.425417896</v>
+        <v>101551618.3547024</v>
       </c>
       <c r="G51">
-        <v>92.22906491674679</v>
-      </c>
-      <c r="H51" t="s">
-        <v>33</v>
+        <v>1488498.682202911</v>
+      </c>
+      <c r="H51">
+        <v>68.22419097100614</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -1813,56 +1819,56 @@
         <v>10</v>
       </c>
       <c r="B52" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C52" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D52" t="s">
-        <v>28</v>
-      </c>
-      <c r="E52">
-        <v>297829386.6468098</v>
+        <v>27</v>
+      </c>
+      <c r="E52" t="s">
+        <v>37</v>
       </c>
       <c r="F52">
-        <v>3237432.425417896</v>
+        <v>119846953.147862</v>
       </c>
       <c r="G52">
-        <v>91.99555311439904</v>
-      </c>
-      <c r="H52" t="s">
-        <v>33</v>
+        <v>1488498.682202911</v>
+      </c>
+      <c r="H52">
+        <v>80.51532364845217</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B53" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C53" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D53" t="s">
-        <v>29</v>
-      </c>
-      <c r="E53">
-        <v>498327252.4789845</v>
+        <v>27</v>
+      </c>
+      <c r="E53" t="s">
+        <v>32</v>
       </c>
       <c r="F53">
-        <v>3237432.425417896</v>
+        <v>16287481.78218056</v>
       </c>
       <c r="G53">
-        <v>153.9266884974932</v>
-      </c>
-      <c r="H53" t="s">
-        <v>33</v>
+        <v>1488498.682202911</v>
+      </c>
+      <c r="H53">
+        <v>10.94222116345835</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B54" t="s">
         <v>15</v>
@@ -1871,24 +1877,24 @@
         <v>21</v>
       </c>
       <c r="D54" t="s">
-        <v>23</v>
-      </c>
-      <c r="E54">
-        <v>27641296.88104996</v>
+        <v>27</v>
+      </c>
+      <c r="E54" t="s">
+        <v>33</v>
       </c>
       <c r="F54">
-        <v>1877045.65071168</v>
+        <v>8994957.46681097</v>
       </c>
       <c r="G54">
-        <v>14.72595878026184</v>
-      </c>
-      <c r="H54" t="s">
-        <v>34</v>
+        <v>1488498.682202911</v>
+      </c>
+      <c r="H54">
+        <v>6.042973080432181</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B55" t="s">
         <v>15</v>
@@ -1897,24 +1903,24 @@
         <v>21</v>
       </c>
       <c r="D55" t="s">
-        <v>24</v>
-      </c>
-      <c r="E55">
-        <v>70988818.1029994</v>
+        <v>27</v>
+      </c>
+      <c r="E55" t="s">
+        <v>34</v>
       </c>
       <c r="F55">
-        <v>1877045.65071168</v>
+        <v>10673433.70533201</v>
       </c>
       <c r="G55">
-        <v>37.81944145902048</v>
-      </c>
-      <c r="H55" t="s">
-        <v>34</v>
+        <v>1488498.682202911</v>
+      </c>
+      <c r="H55">
+        <v>7.170603395856427</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B56" t="s">
         <v>15</v>
@@ -1923,24 +1929,24 @@
         <v>21</v>
       </c>
       <c r="D56" t="s">
-        <v>25</v>
-      </c>
-      <c r="E56">
-        <v>47486042.34854585</v>
+        <v>27</v>
+      </c>
+      <c r="E56" t="s">
+        <v>35</v>
       </c>
       <c r="F56">
-        <v>1877045.65071168</v>
+        <v>14640772.58338168</v>
       </c>
       <c r="G56">
-        <v>25.29828847292102</v>
-      </c>
-      <c r="H56" t="s">
-        <v>34</v>
+        <v>1488498.682202911</v>
+      </c>
+      <c r="H56">
+        <v>9.835932512693924</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B57" t="s">
         <v>15</v>
@@ -1949,24 +1955,24 @@
         <v>21</v>
       </c>
       <c r="D57" t="s">
-        <v>26</v>
-      </c>
-      <c r="E57">
-        <v>79427436.72861613</v>
+        <v>27</v>
+      </c>
+      <c r="E57" t="s">
+        <v>36</v>
       </c>
       <c r="F57">
-        <v>1877045.65071168</v>
+        <v>21618949.76873008</v>
       </c>
       <c r="G57">
-        <v>42.31513319801321</v>
-      </c>
-      <c r="H57" t="s">
-        <v>34</v>
+        <v>1488498.682202911</v>
+      </c>
+      <c r="H57">
+        <v>14.52399657938225</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B58" t="s">
         <v>15</v>
@@ -1977,22 +1983,22 @@
       <c r="D58" t="s">
         <v>27</v>
       </c>
-      <c r="E58">
-        <v>95607742.09259976</v>
+      <c r="E58" t="s">
+        <v>37</v>
       </c>
       <c r="F58">
-        <v>1877045.65071168</v>
+        <v>14862499.75245467</v>
       </c>
       <c r="G58">
-        <v>50.93522475404376</v>
-      </c>
-      <c r="H58" t="s">
-        <v>34</v>
+        <v>1488498.682202911</v>
+      </c>
+      <c r="H58">
+        <v>9.984892785030103</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B59" t="s">
         <v>15</v>
@@ -2001,24 +2007,24 @@
         <v>21</v>
       </c>
       <c r="D59" t="s">
-        <v>28</v>
-      </c>
-      <c r="E59">
-        <v>117002509.0087378</v>
+        <v>27</v>
+      </c>
+      <c r="E59" t="s">
+        <v>32</v>
       </c>
       <c r="F59">
-        <v>1877045.65071168</v>
+        <v>17593734.71344231</v>
       </c>
       <c r="G59">
-        <v>62.33333161842729</v>
-      </c>
-      <c r="H59" t="s">
-        <v>34</v>
+        <v>1488498.682202911</v>
+      </c>
+      <c r="H59">
+        <v>11.81978521298008</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B60" t="s">
         <v>15</v>
@@ -2027,24 +2033,24 @@
         <v>21</v>
       </c>
       <c r="D60" t="s">
-        <v>29</v>
-      </c>
-      <c r="E60">
-        <v>179531974.0332007</v>
+        <v>27</v>
+      </c>
+      <c r="E60" t="s">
+        <v>33</v>
       </c>
       <c r="F60">
-        <v>1877045.65071168</v>
+        <v>9947879.031872991</v>
       </c>
       <c r="G60">
-        <v>95.64603501525458</v>
-      </c>
-      <c r="H60" t="s">
-        <v>34</v>
+        <v>1488498.682202911</v>
+      </c>
+      <c r="H60">
+        <v>6.68316280747429</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B61" t="s">
         <v>15</v>
@@ -2053,24 +2059,24 @@
         <v>21</v>
       </c>
       <c r="D61" t="s">
-        <v>24</v>
-      </c>
-      <c r="E61">
-        <v>82215590.80432028</v>
+        <v>27</v>
+      </c>
+      <c r="E61" t="s">
+        <v>34</v>
       </c>
       <c r="F61">
-        <v>1877045.65071168</v>
+        <v>11306352.5472976</v>
       </c>
       <c r="G61">
-        <v>43.80052811882774</v>
-      </c>
-      <c r="H61" t="s">
-        <v>34</v>
+        <v>1488498.682202911</v>
+      </c>
+      <c r="H61">
+        <v>7.59580957812116</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B62" t="s">
         <v>15</v>
@@ -2079,24 +2085,24 @@
         <v>21</v>
       </c>
       <c r="D62" t="s">
-        <v>25</v>
-      </c>
-      <c r="E62">
-        <v>59598417.12537961</v>
+        <v>27</v>
+      </c>
+      <c r="E62" t="s">
+        <v>35</v>
       </c>
       <c r="F62">
-        <v>1877045.65071168</v>
+        <v>14347895.96398238</v>
       </c>
       <c r="G62">
-        <v>31.75118149246019</v>
-      </c>
-      <c r="H62" t="s">
-        <v>34</v>
+        <v>1488498.682202911</v>
+      </c>
+      <c r="H62">
+        <v>9.639172768865432</v>
       </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B63" t="s">
         <v>15</v>
@@ -2105,24 +2111,24 @@
         <v>21</v>
       </c>
       <c r="D63" t="s">
-        <v>26</v>
-      </c>
-      <c r="E63">
-        <v>101770759.1934886</v>
+        <v>27</v>
+      </c>
+      <c r="E63" t="s">
+        <v>36</v>
       </c>
       <c r="F63">
-        <v>1877045.65071168</v>
+        <v>24466482.1385634</v>
       </c>
       <c r="G63">
-        <v>54.2185850167801</v>
-      </c>
-      <c r="H63" t="s">
-        <v>34</v>
+        <v>1488498.682202911</v>
+      </c>
+      <c r="H63">
+        <v>16.43701968372192</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B64" t="s">
         <v>15</v>
@@ -2133,74 +2139,74 @@
       <c r="D64" t="s">
         <v>27</v>
       </c>
-      <c r="E64">
-        <v>125709211.348101</v>
+      <c r="E64" t="s">
+        <v>37</v>
       </c>
       <c r="F64">
-        <v>1877045.65071168</v>
+        <v>17419180.29116824</v>
       </c>
       <c r="G64">
-        <v>66.97184551715</v>
-      </c>
-      <c r="H64" t="s">
-        <v>34</v>
+        <v>1488498.682202911</v>
+      </c>
+      <c r="H64">
+        <v>11.70251643447116</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B65" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C65" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D65" t="s">
         <v>28</v>
       </c>
-      <c r="E65">
-        <v>153560351.5188797</v>
+      <c r="E65" t="s">
+        <v>31</v>
       </c>
       <c r="F65">
-        <v>1877045.65071168</v>
+        <v>107009531.6959314</v>
       </c>
       <c r="G65">
-        <v>81.80959874932046</v>
-      </c>
-      <c r="H65" t="s">
-        <v>34</v>
+        <v>3237432.425417896</v>
+      </c>
+      <c r="H65">
+        <v>33.05382711798789</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B66" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C66" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D66" t="s">
-        <v>29</v>
-      </c>
-      <c r="E66">
-        <v>244295631.6727538</v>
+        <v>28</v>
+      </c>
+      <c r="E66" t="s">
+        <v>32</v>
       </c>
       <c r="F66">
-        <v>1877045.65071168</v>
+        <v>201944877.8190014</v>
       </c>
       <c r="G66">
-        <v>130.1490092050395</v>
-      </c>
-      <c r="H66" t="s">
-        <v>34</v>
+        <v>3237432.425417896</v>
+      </c>
+      <c r="H66">
+        <v>62.3780982217517</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B67" t="s">
         <v>16</v>
@@ -2209,19 +2215,19 @@
         <v>22</v>
       </c>
       <c r="D67" t="s">
-        <v>23</v>
-      </c>
-      <c r="E67">
-        <v>9578605.25866594</v>
+        <v>28</v>
+      </c>
+      <c r="E67" t="s">
+        <v>33</v>
       </c>
       <c r="F67">
-        <v>581200.5213831302</v>
+        <v>201512199.3455853</v>
       </c>
       <c r="G67">
-        <v>16.48072378853163</v>
-      </c>
-      <c r="H67" t="s">
-        <v>35</v>
+        <v>3237432.425417896</v>
+      </c>
+      <c r="H67">
+        <v>62.24444957166129</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -2235,19 +2241,19 @@
         <v>22</v>
       </c>
       <c r="D68" t="s">
-        <v>24</v>
-      </c>
-      <c r="E68">
-        <v>23460773.36651546</v>
+        <v>28</v>
+      </c>
+      <c r="E68" t="s">
+        <v>34</v>
       </c>
       <c r="F68">
-        <v>581200.5213831302</v>
+        <v>283203798.3112867</v>
       </c>
       <c r="G68">
-        <v>40.36605698612235</v>
-      </c>
-      <c r="H68" t="s">
-        <v>35</v>
+        <v>3237432.425417896</v>
+      </c>
+      <c r="H68">
+        <v>87.47790257729626</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -2261,19 +2267,19 @@
         <v>22</v>
       </c>
       <c r="D69" t="s">
-        <v>25</v>
-      </c>
-      <c r="E69">
-        <v>23712753.26521241</v>
+        <v>28</v>
+      </c>
+      <c r="E69" t="s">
+        <v>35</v>
       </c>
       <c r="F69">
-        <v>581200.5213831303</v>
+        <v>288357254.3810459</v>
       </c>
       <c r="G69">
-        <v>40.7996076961205</v>
-      </c>
-      <c r="H69" t="s">
-        <v>35</v>
+        <v>3237432.425417896</v>
+      </c>
+      <c r="H69">
+        <v>89.0697369054194</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -2287,19 +2293,19 @@
         <v>22</v>
       </c>
       <c r="D70" t="s">
-        <v>26</v>
-      </c>
-      <c r="E70">
-        <v>29601621.11947902</v>
+        <v>28</v>
+      </c>
+      <c r="E70" t="s">
+        <v>36</v>
       </c>
       <c r="F70">
-        <v>581200.5213831303</v>
+        <v>274266005.9898455</v>
       </c>
       <c r="G70">
-        <v>50.93185575441953</v>
-      </c>
-      <c r="H70" t="s">
-        <v>35</v>
+        <v>3237432.425417896</v>
+      </c>
+      <c r="H70">
+        <v>84.71713690037639</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -2313,24 +2319,24 @@
         <v>22</v>
       </c>
       <c r="D71" t="s">
-        <v>27</v>
-      </c>
-      <c r="E71">
-        <v>31914186.55862749</v>
+        <v>28</v>
+      </c>
+      <c r="E71" t="s">
+        <v>37</v>
       </c>
       <c r="F71">
-        <v>581200.5213831303</v>
+        <v>462637564.4554803</v>
       </c>
       <c r="G71">
-        <v>54.91080166734657</v>
-      </c>
-      <c r="H71" t="s">
-        <v>35</v>
+        <v>3237432.425417896</v>
+      </c>
+      <c r="H71">
+        <v>142.9026165374747</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B72" t="s">
         <v>16</v>
@@ -2341,22 +2347,22 @@
       <c r="D72" t="s">
         <v>28</v>
       </c>
-      <c r="E72">
-        <v>39252277.85010482</v>
+      <c r="E72" t="s">
+        <v>32</v>
       </c>
       <c r="F72">
-        <v>581200.5213831303</v>
+        <v>203565326.0998279</v>
       </c>
       <c r="G72">
-        <v>67.53654961749341</v>
-      </c>
-      <c r="H72" t="s">
-        <v>35</v>
+        <v>3237432.425417896</v>
+      </c>
+      <c r="H72">
+        <v>62.8786332346539</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B73" t="s">
         <v>16</v>
@@ -2365,19 +2371,19 @@
         <v>22</v>
       </c>
       <c r="D73" t="s">
-        <v>29</v>
-      </c>
-      <c r="E73">
-        <v>47617494.16619965</v>
+        <v>28</v>
+      </c>
+      <c r="E73" t="s">
+        <v>33</v>
       </c>
       <c r="F73">
-        <v>581200.5213831303</v>
+        <v>206718927.1378156</v>
       </c>
       <c r="G73">
-        <v>81.92954482022903</v>
-      </c>
-      <c r="H73" t="s">
-        <v>35</v>
+        <v>3237432.425417896</v>
+      </c>
+      <c r="H73">
+        <v>63.8527388293307</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -2391,19 +2397,19 @@
         <v>22</v>
       </c>
       <c r="D74" t="s">
-        <v>24</v>
-      </c>
-      <c r="E74">
-        <v>23901795.38850493</v>
+        <v>28</v>
+      </c>
+      <c r="E74" t="s">
+        <v>34</v>
       </c>
       <c r="F74">
-        <v>581200.5213831302</v>
+        <v>259568173.3052293</v>
       </c>
       <c r="G74">
-        <v>41.12486914434261</v>
-      </c>
-      <c r="H74" t="s">
-        <v>35</v>
+        <v>3237432.425417896</v>
+      </c>
+      <c r="H74">
+        <v>80.17717104063526</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -2417,19 +2423,19 @@
         <v>22</v>
       </c>
       <c r="D75" t="s">
-        <v>25</v>
-      </c>
-      <c r="E75">
-        <v>24687057.98400826</v>
+        <v>28</v>
+      </c>
+      <c r="E75" t="s">
+        <v>35</v>
       </c>
       <c r="F75">
-        <v>581200.5213831303</v>
+        <v>298585365.3274482</v>
       </c>
       <c r="G75">
-        <v>42.47597356805265</v>
-      </c>
-      <c r="H75" t="s">
-        <v>35</v>
+        <v>3237432.425417896</v>
+      </c>
+      <c r="H75">
+        <v>92.22906491674679</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -2443,19 +2449,19 @@
         <v>22</v>
       </c>
       <c r="D76" t="s">
-        <v>26</v>
-      </c>
-      <c r="E76">
-        <v>31124924.16570021</v>
+        <v>28</v>
+      </c>
+      <c r="E76" t="s">
+        <v>36</v>
       </c>
       <c r="F76">
-        <v>581200.5213831303</v>
+        <v>297829386.6468098</v>
       </c>
       <c r="G76">
-        <v>53.55281528590113</v>
-      </c>
-      <c r="H76" t="s">
-        <v>35</v>
+        <v>3237432.425417896</v>
+      </c>
+      <c r="H76">
+        <v>91.99555311439903</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -2469,71 +2475,1007 @@
         <v>22</v>
       </c>
       <c r="D77" t="s">
-        <v>27</v>
-      </c>
-      <c r="E77">
-        <v>34558762.78802476</v>
+        <v>28</v>
+      </c>
+      <c r="E77" t="s">
+        <v>37</v>
       </c>
       <c r="F77">
-        <v>581200.5213831303</v>
+        <v>498327252.4789845</v>
       </c>
       <c r="G77">
-        <v>59.46099756721217</v>
-      </c>
-      <c r="H77" t="s">
-        <v>35</v>
+        <v>3237432.425417896</v>
+      </c>
+      <c r="H77">
+        <v>153.9266884974932</v>
       </c>
     </row>
     <row r="78" spans="1:8">
       <c r="A78" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B78" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C78" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D78" t="s">
-        <v>28</v>
-      </c>
-      <c r="E78">
-        <v>44641867.37223864</v>
+        <v>29</v>
+      </c>
+      <c r="E78" t="s">
+        <v>31</v>
       </c>
       <c r="F78">
-        <v>581200.5213831303</v>
+        <v>27641296.88104996</v>
       </c>
       <c r="G78">
-        <v>76.80975107524121</v>
-      </c>
-      <c r="H78" t="s">
-        <v>35</v>
+        <v>1877045.650711681</v>
+      </c>
+      <c r="H78">
+        <v>14.72595878026184</v>
       </c>
     </row>
     <row r="79" spans="1:8">
       <c r="A79" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B79" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C79" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D79" t="s">
         <v>29</v>
       </c>
-      <c r="E79">
+      <c r="E79" t="s">
+        <v>32</v>
+      </c>
+      <c r="F79">
+        <v>70988818.1029994</v>
+      </c>
+      <c r="G79">
+        <v>1877045.650711681</v>
+      </c>
+      <c r="H79">
+        <v>37.81944145902048</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80" t="s">
+        <v>9</v>
+      </c>
+      <c r="B80" t="s">
+        <v>17</v>
+      </c>
+      <c r="C80" t="s">
+        <v>23</v>
+      </c>
+      <c r="D80" t="s">
+        <v>29</v>
+      </c>
+      <c r="E80" t="s">
+        <v>33</v>
+      </c>
+      <c r="F80">
+        <v>47486042.34854585</v>
+      </c>
+      <c r="G80">
+        <v>1877045.650711681</v>
+      </c>
+      <c r="H80">
+        <v>25.29828847292102</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8">
+      <c r="A81" t="s">
+        <v>9</v>
+      </c>
+      <c r="B81" t="s">
+        <v>17</v>
+      </c>
+      <c r="C81" t="s">
+        <v>23</v>
+      </c>
+      <c r="D81" t="s">
+        <v>29</v>
+      </c>
+      <c r="E81" t="s">
+        <v>34</v>
+      </c>
+      <c r="F81">
+        <v>79427436.72861613</v>
+      </c>
+      <c r="G81">
+        <v>1877045.650711681</v>
+      </c>
+      <c r="H81">
+        <v>42.31513319801321</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
+      <c r="A82" t="s">
+        <v>9</v>
+      </c>
+      <c r="B82" t="s">
+        <v>17</v>
+      </c>
+      <c r="C82" t="s">
+        <v>23</v>
+      </c>
+      <c r="D82" t="s">
+        <v>29</v>
+      </c>
+      <c r="E82" t="s">
+        <v>35</v>
+      </c>
+      <c r="F82">
+        <v>95607742.09259976</v>
+      </c>
+      <c r="G82">
+        <v>1877045.650711681</v>
+      </c>
+      <c r="H82">
+        <v>50.93522475404376</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
+      <c r="A83" t="s">
+        <v>9</v>
+      </c>
+      <c r="B83" t="s">
+        <v>17</v>
+      </c>
+      <c r="C83" t="s">
+        <v>23</v>
+      </c>
+      <c r="D83" t="s">
+        <v>29</v>
+      </c>
+      <c r="E83" t="s">
+        <v>36</v>
+      </c>
+      <c r="F83">
+        <v>117002509.0087378</v>
+      </c>
+      <c r="G83">
+        <v>1877045.650711681</v>
+      </c>
+      <c r="H83">
+        <v>62.33333161842729</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8">
+      <c r="A84" t="s">
+        <v>9</v>
+      </c>
+      <c r="B84" t="s">
+        <v>17</v>
+      </c>
+      <c r="C84" t="s">
+        <v>23</v>
+      </c>
+      <c r="D84" t="s">
+        <v>29</v>
+      </c>
+      <c r="E84" t="s">
+        <v>37</v>
+      </c>
+      <c r="F84">
+        <v>179531974.0332007</v>
+      </c>
+      <c r="G84">
+        <v>1877045.650711681</v>
+      </c>
+      <c r="H84">
+        <v>95.64603501525458</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
+      <c r="A85" t="s">
+        <v>10</v>
+      </c>
+      <c r="B85" t="s">
+        <v>17</v>
+      </c>
+      <c r="C85" t="s">
+        <v>23</v>
+      </c>
+      <c r="D85" t="s">
+        <v>29</v>
+      </c>
+      <c r="E85" t="s">
+        <v>32</v>
+      </c>
+      <c r="F85">
+        <v>82215590.80432028</v>
+      </c>
+      <c r="G85">
+        <v>1877045.650711681</v>
+      </c>
+      <c r="H85">
+        <v>43.80052811882774</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8">
+      <c r="A86" t="s">
+        <v>10</v>
+      </c>
+      <c r="B86" t="s">
+        <v>17</v>
+      </c>
+      <c r="C86" t="s">
+        <v>23</v>
+      </c>
+      <c r="D86" t="s">
+        <v>29</v>
+      </c>
+      <c r="E86" t="s">
+        <v>33</v>
+      </c>
+      <c r="F86">
+        <v>59598417.12537961</v>
+      </c>
+      <c r="G86">
+        <v>1877045.650711681</v>
+      </c>
+      <c r="H86">
+        <v>31.75118149246019</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8">
+      <c r="A87" t="s">
+        <v>10</v>
+      </c>
+      <c r="B87" t="s">
+        <v>17</v>
+      </c>
+      <c r="C87" t="s">
+        <v>23</v>
+      </c>
+      <c r="D87" t="s">
+        <v>29</v>
+      </c>
+      <c r="E87" t="s">
+        <v>34</v>
+      </c>
+      <c r="F87">
+        <v>101770759.1934886</v>
+      </c>
+      <c r="G87">
+        <v>1877045.650711681</v>
+      </c>
+      <c r="H87">
+        <v>54.2185850167801</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8">
+      <c r="A88" t="s">
+        <v>10</v>
+      </c>
+      <c r="B88" t="s">
+        <v>17</v>
+      </c>
+      <c r="C88" t="s">
+        <v>23</v>
+      </c>
+      <c r="D88" t="s">
+        <v>29</v>
+      </c>
+      <c r="E88" t="s">
+        <v>35</v>
+      </c>
+      <c r="F88">
+        <v>125709211.348101</v>
+      </c>
+      <c r="G88">
+        <v>1877045.650711681</v>
+      </c>
+      <c r="H88">
+        <v>66.97184551715</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8">
+      <c r="A89" t="s">
+        <v>10</v>
+      </c>
+      <c r="B89" t="s">
+        <v>17</v>
+      </c>
+      <c r="C89" t="s">
+        <v>23</v>
+      </c>
+      <c r="D89" t="s">
+        <v>29</v>
+      </c>
+      <c r="E89" t="s">
+        <v>36</v>
+      </c>
+      <c r="F89">
+        <v>153560351.5188797</v>
+      </c>
+      <c r="G89">
+        <v>1877045.650711681</v>
+      </c>
+      <c r="H89">
+        <v>81.80959874932046</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8">
+      <c r="A90" t="s">
+        <v>10</v>
+      </c>
+      <c r="B90" t="s">
+        <v>17</v>
+      </c>
+      <c r="C90" t="s">
+        <v>23</v>
+      </c>
+      <c r="D90" t="s">
+        <v>29</v>
+      </c>
+      <c r="E90" t="s">
+        <v>37</v>
+      </c>
+      <c r="F90">
+        <v>244295631.6727538</v>
+      </c>
+      <c r="G90">
+        <v>1877045.650711681</v>
+      </c>
+      <c r="H90">
+        <v>130.1490092050395</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8">
+      <c r="A91" t="s">
+        <v>8</v>
+      </c>
+      <c r="B91" t="s">
+        <v>18</v>
+      </c>
+      <c r="C91" t="s">
+        <v>24</v>
+      </c>
+      <c r="D91" t="s">
+        <v>30</v>
+      </c>
+      <c r="E91" t="s">
+        <v>31</v>
+      </c>
+      <c r="F91">
+        <v>9578605.25866594</v>
+      </c>
+      <c r="G91">
+        <v>581200.5213831302</v>
+      </c>
+      <c r="H91">
+        <v>16.48072378853163</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8">
+      <c r="A92" t="s">
+        <v>9</v>
+      </c>
+      <c r="B92" t="s">
+        <v>18</v>
+      </c>
+      <c r="C92" t="s">
+        <v>24</v>
+      </c>
+      <c r="D92" t="s">
+        <v>30</v>
+      </c>
+      <c r="E92" t="s">
+        <v>32</v>
+      </c>
+      <c r="F92">
+        <v>23460773.36651546</v>
+      </c>
+      <c r="G92">
+        <v>581200.5213831302</v>
+      </c>
+      <c r="H92">
+        <v>40.36605698612235</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8">
+      <c r="A93" t="s">
+        <v>9</v>
+      </c>
+      <c r="B93" t="s">
+        <v>18</v>
+      </c>
+      <c r="C93" t="s">
+        <v>24</v>
+      </c>
+      <c r="D93" t="s">
+        <v>30</v>
+      </c>
+      <c r="E93" t="s">
+        <v>33</v>
+      </c>
+      <c r="F93">
+        <v>23712753.26521241</v>
+      </c>
+      <c r="G93">
+        <v>581200.5213831303</v>
+      </c>
+      <c r="H93">
+        <v>40.7996076961205</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8">
+      <c r="A94" t="s">
+        <v>9</v>
+      </c>
+      <c r="B94" t="s">
+        <v>18</v>
+      </c>
+      <c r="C94" t="s">
+        <v>24</v>
+      </c>
+      <c r="D94" t="s">
+        <v>30</v>
+      </c>
+      <c r="E94" t="s">
+        <v>34</v>
+      </c>
+      <c r="F94">
+        <v>29601621.11947902</v>
+      </c>
+      <c r="G94">
+        <v>581200.5213831303</v>
+      </c>
+      <c r="H94">
+        <v>50.93185575441953</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8">
+      <c r="A95" t="s">
+        <v>9</v>
+      </c>
+      <c r="B95" t="s">
+        <v>18</v>
+      </c>
+      <c r="C95" t="s">
+        <v>24</v>
+      </c>
+      <c r="D95" t="s">
+        <v>30</v>
+      </c>
+      <c r="E95" t="s">
+        <v>35</v>
+      </c>
+      <c r="F95">
+        <v>31914186.55862749</v>
+      </c>
+      <c r="G95">
+        <v>581200.5213831303</v>
+      </c>
+      <c r="H95">
+        <v>54.91080166734657</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8">
+      <c r="A96" t="s">
+        <v>9</v>
+      </c>
+      <c r="B96" t="s">
+        <v>18</v>
+      </c>
+      <c r="C96" t="s">
+        <v>24</v>
+      </c>
+      <c r="D96" t="s">
+        <v>30</v>
+      </c>
+      <c r="E96" t="s">
+        <v>36</v>
+      </c>
+      <c r="F96">
+        <v>39252277.85010482</v>
+      </c>
+      <c r="G96">
+        <v>581200.5213831303</v>
+      </c>
+      <c r="H96">
+        <v>67.53654961749341</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8">
+      <c r="A97" t="s">
+        <v>9</v>
+      </c>
+      <c r="B97" t="s">
+        <v>18</v>
+      </c>
+      <c r="C97" t="s">
+        <v>24</v>
+      </c>
+      <c r="D97" t="s">
+        <v>30</v>
+      </c>
+      <c r="E97" t="s">
+        <v>37</v>
+      </c>
+      <c r="F97">
+        <v>47617494.16619965</v>
+      </c>
+      <c r="G97">
+        <v>581200.5213831303</v>
+      </c>
+      <c r="H97">
+        <v>81.92954482022903</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8">
+      <c r="A98" t="s">
+        <v>10</v>
+      </c>
+      <c r="B98" t="s">
+        <v>18</v>
+      </c>
+      <c r="C98" t="s">
+        <v>24</v>
+      </c>
+      <c r="D98" t="s">
+        <v>30</v>
+      </c>
+      <c r="E98" t="s">
+        <v>32</v>
+      </c>
+      <c r="F98">
+        <v>23901795.38850493</v>
+      </c>
+      <c r="G98">
+        <v>581200.5213831302</v>
+      </c>
+      <c r="H98">
+        <v>41.1248691443426</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8">
+      <c r="A99" t="s">
+        <v>10</v>
+      </c>
+      <c r="B99" t="s">
+        <v>18</v>
+      </c>
+      <c r="C99" t="s">
+        <v>24</v>
+      </c>
+      <c r="D99" t="s">
+        <v>30</v>
+      </c>
+      <c r="E99" t="s">
+        <v>33</v>
+      </c>
+      <c r="F99">
+        <v>24687057.98400826</v>
+      </c>
+      <c r="G99">
+        <v>581200.5213831303</v>
+      </c>
+      <c r="H99">
+        <v>42.47597356805265</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8">
+      <c r="A100" t="s">
+        <v>10</v>
+      </c>
+      <c r="B100" t="s">
+        <v>18</v>
+      </c>
+      <c r="C100" t="s">
+        <v>24</v>
+      </c>
+      <c r="D100" t="s">
+        <v>30</v>
+      </c>
+      <c r="E100" t="s">
+        <v>34</v>
+      </c>
+      <c r="F100">
+        <v>31124924.16570021</v>
+      </c>
+      <c r="G100">
+        <v>581200.5213831303</v>
+      </c>
+      <c r="H100">
+        <v>53.55281528590113</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8">
+      <c r="A101" t="s">
+        <v>10</v>
+      </c>
+      <c r="B101" t="s">
+        <v>18</v>
+      </c>
+      <c r="C101" t="s">
+        <v>24</v>
+      </c>
+      <c r="D101" t="s">
+        <v>30</v>
+      </c>
+      <c r="E101" t="s">
+        <v>35</v>
+      </c>
+      <c r="F101">
+        <v>34558762.78802476</v>
+      </c>
+      <c r="G101">
+        <v>581200.5213831303</v>
+      </c>
+      <c r="H101">
+        <v>59.46099756721217</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8">
+      <c r="A102" t="s">
+        <v>10</v>
+      </c>
+      <c r="B102" t="s">
+        <v>18</v>
+      </c>
+      <c r="C102" t="s">
+        <v>24</v>
+      </c>
+      <c r="D102" t="s">
+        <v>30</v>
+      </c>
+      <c r="E102" t="s">
+        <v>36</v>
+      </c>
+      <c r="F102">
+        <v>44641867.37223864</v>
+      </c>
+      <c r="G102">
+        <v>581200.5213831303</v>
+      </c>
+      <c r="H102">
+        <v>76.80975107524121</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8">
+      <c r="A103" t="s">
+        <v>10</v>
+      </c>
+      <c r="B103" t="s">
+        <v>18</v>
+      </c>
+      <c r="C103" t="s">
+        <v>24</v>
+      </c>
+      <c r="D103" t="s">
+        <v>30</v>
+      </c>
+      <c r="E103" t="s">
+        <v>37</v>
+      </c>
+      <c r="F103">
         <v>55642810.96332396</v>
       </c>
-      <c r="F79">
+      <c r="G103">
         <v>581200.5213831303</v>
       </c>
-      <c r="G79">
+      <c r="H103">
         <v>95.73771687421446</v>
       </c>
-      <c r="H79" t="s">
+    </row>
+    <row r="104" spans="1:8">
+      <c r="A104" t="s">
+        <v>11</v>
+      </c>
+      <c r="B104" t="s">
+        <v>18</v>
+      </c>
+      <c r="C104" t="s">
+        <v>24</v>
+      </c>
+      <c r="D104" t="s">
+        <v>30</v>
+      </c>
+      <c r="E104" t="s">
+        <v>32</v>
+      </c>
+      <c r="F104">
+        <v>4019737.293083158</v>
+      </c>
+      <c r="G104">
+        <v>581200.5213831302</v>
+      </c>
+      <c r="H104">
+        <v>6.916265807052379</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8">
+      <c r="A105" t="s">
+        <v>11</v>
+      </c>
+      <c r="B105" t="s">
+        <v>18</v>
+      </c>
+      <c r="C105" t="s">
+        <v>24</v>
+      </c>
+      <c r="D105" t="s">
+        <v>30</v>
+      </c>
+      <c r="E105" t="s">
+        <v>33</v>
+      </c>
+      <c r="F105">
+        <v>3310455.780870662</v>
+      </c>
+      <c r="G105">
+        <v>581200.5213831303</v>
+      </c>
+      <c r="H105">
+        <v>5.695892655072814</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8">
+      <c r="A106" t="s">
+        <v>11</v>
+      </c>
+      <c r="B106" t="s">
+        <v>18</v>
+      </c>
+      <c r="C106" t="s">
+        <v>24</v>
+      </c>
+      <c r="D106" t="s">
+        <v>30</v>
+      </c>
+      <c r="E106" t="s">
+        <v>34</v>
+      </c>
+      <c r="F106">
+        <v>4702318.727527466</v>
+      </c>
+      <c r="G106">
+        <v>581200.5213831303</v>
+      </c>
+      <c r="H106">
+        <v>8.090699430786769</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8">
+      <c r="A107" t="s">
+        <v>11</v>
+      </c>
+      <c r="B107" t="s">
+        <v>18</v>
+      </c>
+      <c r="C107" t="s">
+        <v>24</v>
+      </c>
+      <c r="D107" t="s">
+        <v>30</v>
+      </c>
+      <c r="E107" t="s">
         <v>35</v>
+      </c>
+      <c r="F107">
+        <v>4885823.676316657</v>
+      </c>
+      <c r="G107">
+        <v>581200.5213831303</v>
+      </c>
+      <c r="H107">
+        <v>8.406433746290288</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8">
+      <c r="A108" t="s">
+        <v>11</v>
+      </c>
+      <c r="B108" t="s">
+        <v>18</v>
+      </c>
+      <c r="C108" t="s">
+        <v>24</v>
+      </c>
+      <c r="D108" t="s">
+        <v>30</v>
+      </c>
+      <c r="E108" t="s">
+        <v>36</v>
+      </c>
+      <c r="F108">
+        <v>6280542.93739988</v>
+      </c>
+      <c r="G108">
+        <v>581200.5213831303</v>
+      </c>
+      <c r="H108">
+        <v>10.80615502968504</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8">
+      <c r="A109" t="s">
+        <v>11</v>
+      </c>
+      <c r="B109" t="s">
+        <v>18</v>
+      </c>
+      <c r="C109" t="s">
+        <v>24</v>
+      </c>
+      <c r="D109" t="s">
+        <v>30</v>
+      </c>
+      <c r="E109" t="s">
+        <v>37</v>
+      </c>
+      <c r="F109">
+        <v>7185428.649122512</v>
+      </c>
+      <c r="G109">
+        <v>581200.5213831303</v>
+      </c>
+      <c r="H109">
+        <v>12.36308018448222</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8">
+      <c r="A110" t="s">
+        <v>12</v>
+      </c>
+      <c r="B110" t="s">
+        <v>18</v>
+      </c>
+      <c r="C110" t="s">
+        <v>24</v>
+      </c>
+      <c r="D110" t="s">
+        <v>30</v>
+      </c>
+      <c r="E110" t="s">
+        <v>32</v>
+      </c>
+      <c r="F110">
+        <v>3873813.459940849</v>
+      </c>
+      <c r="G110">
+        <v>581200.5213831303</v>
+      </c>
+      <c r="H110">
+        <v>6.665192678633562</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8">
+      <c r="A111" t="s">
+        <v>12</v>
+      </c>
+      <c r="B111" t="s">
+        <v>18</v>
+      </c>
+      <c r="C111" t="s">
+        <v>24</v>
+      </c>
+      <c r="D111" t="s">
+        <v>30</v>
+      </c>
+      <c r="E111" t="s">
+        <v>33</v>
+      </c>
+      <c r="F111">
+        <v>3726355.309924745</v>
+      </c>
+      <c r="G111">
+        <v>581200.5213831303</v>
+      </c>
+      <c r="H111">
+        <v>6.411479640549586</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8">
+      <c r="A112" t="s">
+        <v>12</v>
+      </c>
+      <c r="B112" t="s">
+        <v>18</v>
+      </c>
+      <c r="C112" t="s">
+        <v>24</v>
+      </c>
+      <c r="D112" t="s">
+        <v>30</v>
+      </c>
+      <c r="E112" t="s">
+        <v>34</v>
+      </c>
+      <c r="F112">
+        <v>5207537.167814495</v>
+      </c>
+      <c r="G112">
+        <v>581200.5213831303</v>
+      </c>
+      <c r="H112">
+        <v>8.959966442255926</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8">
+      <c r="A113" t="s">
+        <v>12</v>
+      </c>
+      <c r="B113" t="s">
+        <v>18</v>
+      </c>
+      <c r="C113" t="s">
+        <v>24</v>
+      </c>
+      <c r="D113" t="s">
+        <v>30</v>
+      </c>
+      <c r="E113" t="s">
+        <v>35</v>
+      </c>
+      <c r="F113">
+        <v>5107268.991712712</v>
+      </c>
+      <c r="G113">
+        <v>581200.5213831303</v>
+      </c>
+      <c r="H113">
+        <v>8.787447367663274</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8">
+      <c r="A114" t="s">
+        <v>12</v>
+      </c>
+      <c r="B114" t="s">
+        <v>18</v>
+      </c>
+      <c r="C114" t="s">
+        <v>24</v>
+      </c>
+      <c r="D114" t="s">
+        <v>30</v>
+      </c>
+      <c r="E114" t="s">
+        <v>36</v>
+      </c>
+      <c r="F114">
+        <v>7737317.911446427</v>
+      </c>
+      <c r="G114">
+        <v>581200.5213831303</v>
+      </c>
+      <c r="H114">
+        <v>13.31264791888572</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8">
+      <c r="A115" t="s">
+        <v>12</v>
+      </c>
+      <c r="B115" t="s">
+        <v>18</v>
+      </c>
+      <c r="C115" t="s">
+        <v>24</v>
+      </c>
+      <c r="D115" t="s">
+        <v>30</v>
+      </c>
+      <c r="E115" t="s">
+        <v>37</v>
+      </c>
+      <c r="F115">
+        <v>9198722.426902626</v>
+      </c>
+      <c r="G115">
+        <v>581200.5213831303</v>
+      </c>
+      <c r="H115">
+        <v>15.82710628856918</v>
       </c>
     </row>
   </sheetData>

--- a/results/per_capita_hours/per_capita_hours_summary.xlsx
+++ b/results/per_capita_hours/per_capita_hours_summary.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="36">
   <si>
     <t>策略</t>
   </si>
@@ -47,12 +47,6 @@
   </si>
   <si>
     <t>定容</t>
-  </si>
-  <si>
-    <t>扩容_26C</t>
-  </si>
-  <si>
-    <t>定容_26C</t>
   </si>
   <si>
     <t>北京市</t>
@@ -485,7 +479,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H115"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -519,25 +513,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F2">
-        <v>6084353.362053598</v>
+        <v>6240706.401166206</v>
       </c>
       <c r="G2">
         <v>5900281.724590417</v>
       </c>
       <c r="H2">
-        <v>1.031197092961855</v>
+        <v>1.05769634272835</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -545,25 +539,25 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F3">
-        <v>11503824.4077344</v>
+        <v>12000442.97403466</v>
       </c>
       <c r="G3">
         <v>5900281.724590418</v>
       </c>
       <c r="H3">
-        <v>1.949707648668754</v>
+        <v>2.033876267979</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -571,25 +565,25 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F4">
-        <v>16088522.54070038</v>
+        <v>16779884.63574051</v>
       </c>
       <c r="G4">
         <v>5900281.724590417</v>
       </c>
       <c r="H4">
-        <v>2.726738025685918</v>
+        <v>2.843912446723945</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -597,25 +591,25 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F5">
-        <v>26019349.75405014</v>
+        <v>27188536.9313821</v>
       </c>
       <c r="G5">
-        <v>5900281.724590417</v>
+        <v>5900281.724590418</v>
       </c>
       <c r="H5">
-        <v>4.409848710377696</v>
+        <v>4.608006566545678</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -623,25 +617,25 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F6">
-        <v>36290181.92474034</v>
+        <v>36941630.90172031</v>
       </c>
       <c r="G6">
         <v>5900281.724590417</v>
       </c>
       <c r="H6">
-        <v>6.150584602341089</v>
+        <v>6.260994411124446</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -649,25 +643,25 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F7">
-        <v>40289854.07210815</v>
+        <v>41276160.8759262</v>
       </c>
       <c r="G7">
         <v>5900281.724590417</v>
       </c>
       <c r="H7">
-        <v>6.828462767157948</v>
+        <v>6.995625429867331</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -675,25 +669,25 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F8">
-        <v>92927897.47736895</v>
+        <v>96964558.88244542</v>
       </c>
       <c r="G8">
-        <v>5900281.724590417</v>
+        <v>5900281.724590418</v>
       </c>
       <c r="H8">
-        <v>15.74973904891292</v>
+        <v>16.43388628009562</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -701,25 +695,25 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F9">
-        <v>12105154.88352069</v>
+        <v>12610251.82243834</v>
       </c>
       <c r="G9">
-        <v>5900281.724590417</v>
+        <v>5900281.724590418</v>
       </c>
       <c r="H9">
-        <v>2.05162320183296</v>
+        <v>2.137228764837277</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -727,25 +721,25 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E10" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F10">
-        <v>21292652.95341992</v>
+        <v>22002850.7258377</v>
       </c>
       <c r="G10">
         <v>5900281.724590417</v>
       </c>
       <c r="H10">
-        <v>3.608751911739944</v>
+        <v>3.729118668035311</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -753,25 +747,25 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E11" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F11">
-        <v>27655595.63203176</v>
+        <v>28817179.66371435</v>
       </c>
       <c r="G11">
         <v>5900281.724590417</v>
       </c>
       <c r="H11">
-        <v>4.687165278358221</v>
+        <v>4.884034527302977</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -779,25 +773,25 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F12">
-        <v>49072616.18256301</v>
+        <v>50038201.36269932</v>
       </c>
       <c r="G12">
-        <v>5900281.724590418</v>
+        <v>5900281.724590417</v>
       </c>
       <c r="H12">
-        <v>8.316995437361003</v>
+        <v>8.480646128159728</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -805,25 +799,25 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D13" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E13" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F13">
-        <v>45499452.97391333</v>
+        <v>46871358.57576589</v>
       </c>
       <c r="G13">
         <v>5900281.724590417</v>
       </c>
       <c r="H13">
-        <v>7.711403471513352</v>
+        <v>7.943918742120671</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -831,25 +825,25 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E14" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F14">
-        <v>155793777.8074042</v>
+        <v>162000392.4588686</v>
       </c>
       <c r="G14">
         <v>5900281.724590417</v>
       </c>
       <c r="H14">
-        <v>26.40446424076792</v>
+        <v>27.45638259673342</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -857,25 +851,25 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C15" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D15" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E15" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F15">
-        <v>47310862.42603313</v>
+        <v>48270164.89642763</v>
       </c>
       <c r="G15">
         <v>4875767.960493487</v>
       </c>
       <c r="H15">
-        <v>9.703263733913353</v>
+        <v>9.900012733900098</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -883,25 +877,25 @@
         <v>9</v>
       </c>
       <c r="B16" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D16" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E16" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F16">
-        <v>249832938.8970911</v>
+        <v>251202904.7250491</v>
       </c>
       <c r="G16">
         <v>4875767.960493487</v>
       </c>
       <c r="H16">
-        <v>51.23971052794009</v>
+        <v>51.52068489732319</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -909,25 +903,25 @@
         <v>9</v>
       </c>
       <c r="B17" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C17" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D17" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E17" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F17">
-        <v>124164578.7435003</v>
+        <v>124441206.1083353</v>
       </c>
       <c r="G17">
         <v>4875767.960493487</v>
       </c>
       <c r="H17">
-        <v>25.46564556590042</v>
+        <v>25.5223807032319</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -935,25 +929,25 @@
         <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C18" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E18" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F18">
-        <v>166114106.8393903</v>
+        <v>167219007.2268224</v>
       </c>
       <c r="G18">
         <v>4875767.960493487</v>
       </c>
       <c r="H18">
-        <v>34.06932163001816</v>
+        <v>34.29593216529891</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -961,25 +955,25 @@
         <v>9</v>
       </c>
       <c r="B19" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C19" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E19" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F19">
-        <v>297684815.1021526</v>
+        <v>301335204.3163406</v>
       </c>
       <c r="G19">
         <v>4875767.960493487</v>
       </c>
       <c r="H19">
-        <v>61.05393396777301</v>
+        <v>61.80261381549457</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -987,25 +981,25 @@
         <v>9</v>
       </c>
       <c r="B20" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C20" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D20" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E20" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F20">
-        <v>336275644.4580898</v>
+        <v>338011099.3954629</v>
       </c>
       <c r="G20">
         <v>4875767.960493487</v>
       </c>
       <c r="H20">
-        <v>68.96875470342411</v>
+        <v>69.32468938928999</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1013,25 +1007,25 @@
         <v>9</v>
       </c>
       <c r="B21" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C21" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D21" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E21" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F21">
-        <v>548319631.2929255</v>
+        <v>548669598.3561199</v>
       </c>
       <c r="G21">
         <v>4875767.960493487</v>
       </c>
       <c r="H21">
-        <v>112.458106237982</v>
+        <v>112.5298830464828</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1039,25 +1033,25 @@
         <v>10</v>
       </c>
       <c r="B22" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C22" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D22" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E22" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F22">
-        <v>282264703.3045797</v>
+        <v>284476637.2697743</v>
       </c>
       <c r="G22">
         <v>4875767.960493487</v>
       </c>
       <c r="H22">
-        <v>57.89133231762962</v>
+        <v>58.34499089677388</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1065,25 +1059,25 @@
         <v>10</v>
       </c>
       <c r="B23" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C23" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D23" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E23" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F23">
-        <v>130465411.2634157</v>
+        <v>131137651.5815994</v>
       </c>
       <c r="G23">
         <v>4875767.960493487</v>
       </c>
       <c r="H23">
-        <v>26.75792045899801</v>
+        <v>26.89579418958375</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1091,25 +1085,25 @@
         <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C24" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D24" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E24" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F24">
-        <v>178571061.5903344</v>
+        <v>179777609.077431</v>
       </c>
       <c r="G24">
         <v>4875767.960493487</v>
       </c>
       <c r="H24">
-        <v>36.62419192981054</v>
+        <v>36.87164986810309</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1117,25 +1111,25 @@
         <v>10</v>
       </c>
       <c r="B25" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C25" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D25" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E25" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F25">
-        <v>368023062.0423386</v>
+        <v>371871351.1063213</v>
       </c>
       <c r="G25">
         <v>4875767.960493487</v>
       </c>
       <c r="H25">
-        <v>75.48001976802239</v>
+        <v>76.26928806281491</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1143,25 +1137,25 @@
         <v>10</v>
       </c>
       <c r="B26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C26" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D26" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E26" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F26">
-        <v>436178785.8196998</v>
+        <v>437714015.6131574</v>
       </c>
       <c r="G26">
         <v>4875767.960493487</v>
       </c>
       <c r="H26">
-        <v>89.45847902400038</v>
+        <v>89.77334835451344</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1169,389 +1163,389 @@
         <v>10</v>
       </c>
       <c r="B27" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C27" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D27" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E27" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F27">
-        <v>698710388.1267633</v>
+        <v>699174128.6019485</v>
       </c>
       <c r="G27">
         <v>4875767.960493487</v>
       </c>
       <c r="H27">
-        <v>143.3026333057993</v>
+        <v>143.3977445742073</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B28" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C28" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D28" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E28" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F28">
-        <v>23345430.00312043</v>
+        <v>25167587.86489875</v>
       </c>
       <c r="G28">
-        <v>4875767.960493487</v>
+        <v>1488498.682202911</v>
       </c>
       <c r="H28">
-        <v>4.788051890959467</v>
+        <v>16.90803503275653</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B29" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C29" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D29" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E29" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F29">
-        <v>7915098.399554222</v>
+        <v>74022142.65882272</v>
       </c>
       <c r="G29">
-        <v>4875767.960493487</v>
+        <v>1488498.682202911</v>
       </c>
       <c r="H29">
-        <v>1.623354200545901</v>
+        <v>49.72939750895396</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B30" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C30" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E30" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F30">
-        <v>11495400.35526426</v>
+        <v>57181720.09318546</v>
       </c>
       <c r="G30">
-        <v>4875767.960493487</v>
+        <v>1488498.682202911</v>
       </c>
       <c r="H30">
-        <v>2.357659439170848</v>
+        <v>38.41570085138341</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B31" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C31" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D31" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E31" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F31">
-        <v>20092878.12114714</v>
+        <v>59436313.39123303</v>
       </c>
       <c r="G31">
-        <v>4875767.960493487</v>
+        <v>1488498.682202911</v>
       </c>
       <c r="H31">
-        <v>4.120966847469398</v>
+        <v>39.9303768971229</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B32" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C32" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D32" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E32" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F32">
-        <v>24361804.36527121</v>
+        <v>79530650.97178617</v>
       </c>
       <c r="G32">
-        <v>4875767.960493487</v>
+        <v>1488498.682202911</v>
       </c>
       <c r="H32">
-        <v>4.996506101739405</v>
+        <v>53.43011177818738</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B33" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C33" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D33" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E33" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F33">
-        <v>53401501.13574702</v>
+        <v>93782960.82160889</v>
       </c>
       <c r="G33">
-        <v>4875767.960493487</v>
+        <v>1488498.682202911</v>
       </c>
       <c r="H33">
-        <v>10.95242873911131</v>
+        <v>63.00506808834677</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B34" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C34" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D34" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E34" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F34">
-        <v>40309054.98713735</v>
+        <v>105205951.7959697</v>
       </c>
       <c r="G34">
-        <v>4875767.960493487</v>
+        <v>1488498.682202911</v>
       </c>
       <c r="H34">
-        <v>8.267221761524841</v>
+        <v>70.67923744498694</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B35" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C35" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D35" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E35" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F35">
-        <v>8671326.41632206</v>
+        <v>79922569.19465432</v>
       </c>
       <c r="G35">
-        <v>4875767.960493487</v>
+        <v>1488498.682202911</v>
       </c>
       <c r="H35">
-        <v>1.778453463450795</v>
+        <v>53.6934094401565</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B36" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C36" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D36" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E36" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F36">
-        <v>11013934.35343651</v>
+        <v>61766266.52293781</v>
       </c>
       <c r="G36">
-        <v>4875767.960493487</v>
+        <v>1488498.682202911</v>
       </c>
       <c r="H36">
-        <v>2.258912737988821</v>
+        <v>41.49568102507588</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B37" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C37" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D37" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E37" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F37">
-        <v>29679366.18381804</v>
+        <v>62213081.00389005</v>
       </c>
       <c r="G37">
-        <v>4875767.960493487</v>
+        <v>1488498.682202911</v>
       </c>
       <c r="H37">
-        <v>6.087116209035945</v>
+        <v>41.79585897369924</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B38" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C38" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D38" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E38" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F38">
-        <v>36406925.52336985</v>
+        <v>83717361.68954626</v>
       </c>
       <c r="G38">
-        <v>4875767.960493487</v>
+        <v>1488498.682202911</v>
       </c>
       <c r="H38">
-        <v>7.466911021681398</v>
+        <v>56.24281881502797</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B39" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C39" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D39" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E39" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F39">
-        <v>115498270.7454035</v>
+        <v>102845171.9042636</v>
       </c>
       <c r="G39">
-        <v>4875767.960493487</v>
+        <v>1488498.682202911</v>
       </c>
       <c r="H39">
-        <v>23.68822135943353</v>
+        <v>69.09322334908441</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B40" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C40" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D40" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E40" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F40">
-        <v>25047504.80641522</v>
+        <v>126129203.164016</v>
       </c>
       <c r="G40">
         <v>1488498.682202911</v>
       </c>
       <c r="H40">
-        <v>16.82736108932662</v>
+        <v>84.73585141328472</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B41" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C41" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D41" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E41" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F41">
-        <v>74034829.4328794</v>
+        <v>106735151.8030157</v>
       </c>
       <c r="G41">
-        <v>1488498.682202911</v>
+        <v>3237432.425417896</v>
       </c>
       <c r="H41">
-        <v>49.73792071035707</v>
+        <v>32.96907480292443</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1559,25 +1553,25 @@
         <v>9</v>
       </c>
       <c r="B42" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C42" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D42" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E42" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F42">
-        <v>54358480.9799815</v>
+        <v>201689696.1093711</v>
       </c>
       <c r="G42">
-        <v>1488498.682202911</v>
+        <v>3237432.425417896</v>
       </c>
       <c r="H42">
-        <v>36.51899839073648</v>
+        <v>62.29927597124641</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1585,25 +1579,25 @@
         <v>9</v>
       </c>
       <c r="B43" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C43" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D43" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E43" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F43">
-        <v>59508823.20942345</v>
+        <v>213555377.4857488</v>
       </c>
       <c r="G43">
-        <v>1488498.682202911</v>
+        <v>3237432.425417896</v>
       </c>
       <c r="H43">
-        <v>39.97909028804315</v>
+        <v>65.96442780058412</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -1611,25 +1605,25 @@
         <v>9</v>
       </c>
       <c r="B44" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C44" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D44" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E44" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F44">
-        <v>78972639.79064965</v>
+        <v>282860292.9279305</v>
       </c>
       <c r="G44">
-        <v>1488498.682202911</v>
+        <v>3237432.425417896</v>
       </c>
       <c r="H44">
-        <v>53.05522990035415</v>
+        <v>87.37179831372639</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -1637,25 +1631,25 @@
         <v>9</v>
       </c>
       <c r="B45" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C45" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D45" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E45" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F45">
-        <v>92542070.43296187</v>
+        <v>290119900.7156438</v>
       </c>
       <c r="G45">
-        <v>1488498.682202911</v>
+        <v>3237432.425417896</v>
       </c>
       <c r="H45">
-        <v>62.17141576235979</v>
+        <v>89.61419501387564</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -1663,51 +1657,51 @@
         <v>9</v>
       </c>
       <c r="B46" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C46" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D46" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E46" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F46">
-        <v>98942739.24104676</v>
+        <v>277466901.8566096</v>
       </c>
       <c r="G46">
-        <v>1488498.682202911</v>
+        <v>3237432.425417896</v>
       </c>
       <c r="H46">
-        <v>66.47149938662756</v>
+        <v>85.70585124129454</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B47" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C47" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D47" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E47" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F47">
-        <v>80041703.25937352</v>
+        <v>489086329.8777655</v>
       </c>
       <c r="G47">
-        <v>1488498.682202911</v>
+        <v>3237432.425417896</v>
       </c>
       <c r="H47">
-        <v>53.77344583262605</v>
+        <v>151.0722898917753</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -1715,25 +1709,25 @@
         <v>10</v>
       </c>
       <c r="B48" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C48" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D48" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E48" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F48">
-        <v>59195277.33716299</v>
+        <v>203431165.0253613</v>
       </c>
       <c r="G48">
-        <v>1488498.682202911</v>
+        <v>3237432.425417896</v>
       </c>
       <c r="H48">
-        <v>39.76844457097982</v>
+        <v>62.8371926555662</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -1741,25 +1735,25 @@
         <v>10</v>
       </c>
       <c r="B49" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C49" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D49" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E49" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F49">
-        <v>62335381.75197408</v>
+        <v>219037338.0238893</v>
       </c>
       <c r="G49">
-        <v>1488498.682202911</v>
+        <v>3237432.425417896</v>
       </c>
       <c r="H49">
-        <v>41.87802280061176</v>
+        <v>67.65773280831193</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -1767,25 +1761,25 @@
         <v>10</v>
       </c>
       <c r="B50" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C50" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D50" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E50" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F50">
-        <v>83142580.03190084</v>
+        <v>258921272.3039561</v>
       </c>
       <c r="G50">
-        <v>1488498.682202911</v>
+        <v>3237432.425417896</v>
       </c>
       <c r="H50">
-        <v>55.85667023154736</v>
+        <v>79.9773518888302</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -1793,25 +1787,25 @@
         <v>10</v>
       </c>
       <c r="B51" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C51" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D51" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E51" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F51">
-        <v>101551618.3547024</v>
+        <v>300322655.7685589</v>
       </c>
       <c r="G51">
-        <v>1488498.682202911</v>
+        <v>3237432.425417896</v>
       </c>
       <c r="H51">
-        <v>68.22419097100614</v>
+        <v>92.7656909255156</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -1819,56 +1813,56 @@
         <v>10</v>
       </c>
       <c r="B52" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C52" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D52" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E52" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F52">
-        <v>119846953.147862</v>
+        <v>300799617.2425445</v>
       </c>
       <c r="G52">
-        <v>1488498.682202911</v>
+        <v>3237432.425417896</v>
       </c>
       <c r="H52">
-        <v>80.51532364845217</v>
+        <v>92.91301800800258</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B53" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C53" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D53" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E53" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F53">
-        <v>16287481.78218056</v>
+        <v>523926758.6767684</v>
       </c>
       <c r="G53">
-        <v>1488498.682202911</v>
+        <v>3237432.425417896</v>
       </c>
       <c r="H53">
-        <v>10.94222116345835</v>
+        <v>161.8340369248444</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B54" t="s">
         <v>15</v>
@@ -1880,21 +1874,21 @@
         <v>27</v>
       </c>
       <c r="E54" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F54">
-        <v>8994957.46681097</v>
+        <v>28039037.09605257</v>
       </c>
       <c r="G54">
-        <v>1488498.682202911</v>
+        <v>1877045.650711681</v>
       </c>
       <c r="H54">
-        <v>6.042973080432181</v>
+        <v>14.93785571247113</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B55" t="s">
         <v>15</v>
@@ -1906,21 +1900,21 @@
         <v>27</v>
       </c>
       <c r="E55" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F55">
-        <v>10673433.70533201</v>
+        <v>71257422.68978098</v>
       </c>
       <c r="G55">
-        <v>1488498.682202911</v>
+        <v>1877045.650711681</v>
       </c>
       <c r="H55">
-        <v>7.170603395856427</v>
+        <v>37.96254111495039</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B56" t="s">
         <v>15</v>
@@ -1932,21 +1926,21 @@
         <v>27</v>
       </c>
       <c r="E56" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F56">
-        <v>14640772.58338168</v>
+        <v>50026606.64975322</v>
       </c>
       <c r="G56">
-        <v>1488498.682202911</v>
+        <v>1877045.650711681</v>
       </c>
       <c r="H56">
-        <v>9.835932512693924</v>
+        <v>26.65177942304475</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B57" t="s">
         <v>15</v>
@@ -1958,21 +1952,21 @@
         <v>27</v>
       </c>
       <c r="E57" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F57">
-        <v>21618949.76873008</v>
+        <v>79986039.12870094</v>
       </c>
       <c r="G57">
-        <v>1488498.682202911</v>
+        <v>1877045.650711681</v>
       </c>
       <c r="H57">
-        <v>14.52399657938225</v>
+        <v>42.61272979608903</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B58" t="s">
         <v>15</v>
@@ -1984,21 +1978,21 @@
         <v>27</v>
       </c>
       <c r="E58" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F58">
-        <v>14862499.75245467</v>
+        <v>97121407.06487495</v>
       </c>
       <c r="G58">
-        <v>1488498.682202911</v>
+        <v>1877045.650711681</v>
       </c>
       <c r="H58">
-        <v>9.984892785030103</v>
+        <v>51.74163293687153</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B59" t="s">
         <v>15</v>
@@ -2010,21 +2004,21 @@
         <v>27</v>
       </c>
       <c r="E59" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F59">
-        <v>17593734.71344231</v>
+        <v>120910337.1422888</v>
       </c>
       <c r="G59">
-        <v>1488498.682202911</v>
+        <v>1877045.650711681</v>
       </c>
       <c r="H59">
-        <v>11.81978521298008</v>
+        <v>64.41523523759038</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B60" t="s">
         <v>15</v>
@@ -2036,21 +2030,21 @@
         <v>27</v>
       </c>
       <c r="E60" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F60">
-        <v>9947879.031872991</v>
+        <v>184267426.7457868</v>
       </c>
       <c r="G60">
-        <v>1488498.682202911</v>
+        <v>1877045.650711681</v>
       </c>
       <c r="H60">
-        <v>6.68316280747429</v>
+        <v>98.16885736152554</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B61" t="s">
         <v>15</v>
@@ -2062,21 +2056,21 @@
         <v>27</v>
       </c>
       <c r="E61" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F61">
-        <v>11306352.5472976</v>
+        <v>82579525.10955502</v>
       </c>
       <c r="G61">
-        <v>1488498.682202911</v>
+        <v>1877045.650711681</v>
       </c>
       <c r="H61">
-        <v>7.59580957812116</v>
+        <v>43.99441488183574</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B62" t="s">
         <v>15</v>
@@ -2088,21 +2082,21 @@
         <v>27</v>
       </c>
       <c r="E62" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F62">
-        <v>14347895.96398238</v>
+        <v>61700612.56563159</v>
       </c>
       <c r="G62">
-        <v>1488498.682202911</v>
+        <v>1877045.650711681</v>
       </c>
       <c r="H62">
-        <v>9.639172768865432</v>
+        <v>32.87113051418746</v>
       </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B63" t="s">
         <v>15</v>
@@ -2114,21 +2108,21 @@
         <v>27</v>
       </c>
       <c r="E63" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F63">
-        <v>24466482.1385634</v>
+        <v>102123543.5051462</v>
       </c>
       <c r="G63">
-        <v>1488498.682202911</v>
+        <v>1877045.650711681</v>
       </c>
       <c r="H63">
-        <v>16.43701968372192</v>
+        <v>54.40653159736746</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B64" t="s">
         <v>15</v>
@@ -2140,73 +2134,73 @@
         <v>27</v>
       </c>
       <c r="E64" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F64">
-        <v>17419180.29116824</v>
+        <v>127176921.0997139</v>
       </c>
       <c r="G64">
-        <v>1488498.682202911</v>
+        <v>1877045.650711681</v>
       </c>
       <c r="H64">
-        <v>11.70251643447116</v>
+        <v>67.75377095996299</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B65" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C65" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D65" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E65" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F65">
-        <v>107009531.6959314</v>
+        <v>157765591.4333886</v>
       </c>
       <c r="G65">
-        <v>3237432.425417896</v>
+        <v>1877045.650711681</v>
       </c>
       <c r="H65">
-        <v>33.05382711798789</v>
+        <v>84.04994911741859</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B66" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C66" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D66" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E66" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F66">
-        <v>201944877.8190014</v>
+        <v>249040525.4330169</v>
       </c>
       <c r="G66">
-        <v>3237432.425417896</v>
+        <v>1877045.650711681</v>
       </c>
       <c r="H66">
-        <v>62.3780982217517</v>
+        <v>132.6768612892251</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B67" t="s">
         <v>16</v>
@@ -2218,16 +2212,16 @@
         <v>28</v>
       </c>
       <c r="E67" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F67">
-        <v>201512199.3455853</v>
+        <v>9611853.890797934</v>
       </c>
       <c r="G67">
-        <v>3237432.425417896</v>
+        <v>581200.5213831303</v>
       </c>
       <c r="H67">
-        <v>62.24444957166129</v>
+        <v>16.53793060598745</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -2244,16 +2238,16 @@
         <v>28</v>
       </c>
       <c r="E68" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F68">
-        <v>283203798.3112867</v>
+        <v>23537614.43377975</v>
       </c>
       <c r="G68">
-        <v>3237432.425417896</v>
+        <v>581200.5213831302</v>
       </c>
       <c r="H68">
-        <v>87.47790257729626</v>
+        <v>40.49826792612878</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -2270,16 +2264,16 @@
         <v>28</v>
       </c>
       <c r="E69" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F69">
-        <v>288357254.3810459</v>
+        <v>24043301.39199234</v>
       </c>
       <c r="G69">
-        <v>3237432.425417896</v>
+        <v>581200.5213831303</v>
       </c>
       <c r="H69">
-        <v>89.0697369054194</v>
+        <v>41.36834105856364</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -2296,16 +2290,16 @@
         <v>28</v>
       </c>
       <c r="E70" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F70">
-        <v>274266005.9898455</v>
+        <v>29705670.82749488</v>
       </c>
       <c r="G70">
-        <v>3237432.425417896</v>
+        <v>581200.5213831303</v>
       </c>
       <c r="H70">
-        <v>84.71713690037639</v>
+        <v>51.11088124422509</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -2322,21 +2316,21 @@
         <v>28</v>
       </c>
       <c r="E71" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F71">
-        <v>462637564.4554803</v>
+        <v>32301700.19586874</v>
       </c>
       <c r="G71">
-        <v>3237432.425417896</v>
+        <v>581200.5213831303</v>
       </c>
       <c r="H71">
-        <v>142.9026165374747</v>
+        <v>55.57754855243031</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B72" t="s">
         <v>16</v>
@@ -2348,21 +2342,21 @@
         <v>28</v>
       </c>
       <c r="E72" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F72">
-        <v>203565326.0998279</v>
+        <v>39875542.95589899</v>
       </c>
       <c r="G72">
-        <v>3237432.425417896</v>
+        <v>581200.5213831303</v>
       </c>
       <c r="H72">
-        <v>62.8786332346539</v>
+        <v>68.60892495588942</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B73" t="s">
         <v>16</v>
@@ -2374,16 +2368,16 @@
         <v>28</v>
       </c>
       <c r="E73" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F73">
-        <v>206718927.1378156</v>
+        <v>48634074.77448445</v>
       </c>
       <c r="G73">
-        <v>3237432.425417896</v>
+        <v>581200.5213831303</v>
       </c>
       <c r="H73">
-        <v>63.8527388293307</v>
+        <v>83.6786495971235</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -2400,16 +2394,16 @@
         <v>28</v>
       </c>
       <c r="E74" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F74">
-        <v>259568173.3052293</v>
+        <v>24058847.09306264</v>
       </c>
       <c r="G74">
-        <v>3237432.425417896</v>
+        <v>581200.5213831302</v>
       </c>
       <c r="H74">
-        <v>80.17717104063526</v>
+        <v>41.3950886276011</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -2426,16 +2420,16 @@
         <v>28</v>
       </c>
       <c r="E75" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F75">
-        <v>298585365.3274482</v>
+        <v>25130380.62437433</v>
       </c>
       <c r="G75">
-        <v>3237432.425417896</v>
+        <v>581200.5213831303</v>
       </c>
       <c r="H75">
-        <v>92.22906491674679</v>
+        <v>43.23874411634992</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -2452,16 +2446,16 @@
         <v>28</v>
       </c>
       <c r="E76" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F76">
-        <v>297829386.6468098</v>
+        <v>31292978.57426723</v>
       </c>
       <c r="G76">
-        <v>3237432.425417896</v>
+        <v>581200.5213831303</v>
       </c>
       <c r="H76">
-        <v>91.99555311439903</v>
+        <v>53.84196576389294</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -2478,1004 +2472,68 @@
         <v>28</v>
       </c>
       <c r="E77" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F77">
-        <v>498327252.4789845</v>
+        <v>34841162.98658558</v>
       </c>
       <c r="G77">
-        <v>3237432.425417896</v>
+        <v>581200.5213831303</v>
       </c>
       <c r="H77">
-        <v>153.9266884974932</v>
+        <v>59.94688873243131</v>
       </c>
     </row>
     <row r="78" spans="1:8">
       <c r="A78" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B78" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C78" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D78" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E78" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F78">
-        <v>27641296.88104996</v>
+        <v>45364412.37610775</v>
       </c>
       <c r="G78">
-        <v>1877045.650711681</v>
+        <v>581200.5213831303</v>
       </c>
       <c r="H78">
-        <v>14.72595878026184</v>
+        <v>78.05294508021149</v>
       </c>
     </row>
     <row r="79" spans="1:8">
       <c r="A79" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B79" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C79" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D79" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E79" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F79">
-        <v>70988818.1029994</v>
+        <v>56751683.47514104</v>
       </c>
       <c r="G79">
-        <v>1877045.650711681</v>
+        <v>581200.5213831303</v>
       </c>
       <c r="H79">
-        <v>37.81944145902048</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8">
-      <c r="A80" t="s">
-        <v>9</v>
-      </c>
-      <c r="B80" t="s">
-        <v>17</v>
-      </c>
-      <c r="C80" t="s">
-        <v>23</v>
-      </c>
-      <c r="D80" t="s">
-        <v>29</v>
-      </c>
-      <c r="E80" t="s">
-        <v>33</v>
-      </c>
-      <c r="F80">
-        <v>47486042.34854585</v>
-      </c>
-      <c r="G80">
-        <v>1877045.650711681</v>
-      </c>
-      <c r="H80">
-        <v>25.29828847292102</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8">
-      <c r="A81" t="s">
-        <v>9</v>
-      </c>
-      <c r="B81" t="s">
-        <v>17</v>
-      </c>
-      <c r="C81" t="s">
-        <v>23</v>
-      </c>
-      <c r="D81" t="s">
-        <v>29</v>
-      </c>
-      <c r="E81" t="s">
-        <v>34</v>
-      </c>
-      <c r="F81">
-        <v>79427436.72861613</v>
-      </c>
-      <c r="G81">
-        <v>1877045.650711681</v>
-      </c>
-      <c r="H81">
-        <v>42.31513319801321</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8">
-      <c r="A82" t="s">
-        <v>9</v>
-      </c>
-      <c r="B82" t="s">
-        <v>17</v>
-      </c>
-      <c r="C82" t="s">
-        <v>23</v>
-      </c>
-      <c r="D82" t="s">
-        <v>29</v>
-      </c>
-      <c r="E82" t="s">
-        <v>35</v>
-      </c>
-      <c r="F82">
-        <v>95607742.09259976</v>
-      </c>
-      <c r="G82">
-        <v>1877045.650711681</v>
-      </c>
-      <c r="H82">
-        <v>50.93522475404376</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8">
-      <c r="A83" t="s">
-        <v>9</v>
-      </c>
-      <c r="B83" t="s">
-        <v>17</v>
-      </c>
-      <c r="C83" t="s">
-        <v>23</v>
-      </c>
-      <c r="D83" t="s">
-        <v>29</v>
-      </c>
-      <c r="E83" t="s">
-        <v>36</v>
-      </c>
-      <c r="F83">
-        <v>117002509.0087378</v>
-      </c>
-      <c r="G83">
-        <v>1877045.650711681</v>
-      </c>
-      <c r="H83">
-        <v>62.33333161842729</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8">
-      <c r="A84" t="s">
-        <v>9</v>
-      </c>
-      <c r="B84" t="s">
-        <v>17</v>
-      </c>
-      <c r="C84" t="s">
-        <v>23</v>
-      </c>
-      <c r="D84" t="s">
-        <v>29</v>
-      </c>
-      <c r="E84" t="s">
-        <v>37</v>
-      </c>
-      <c r="F84">
-        <v>179531974.0332007</v>
-      </c>
-      <c r="G84">
-        <v>1877045.650711681</v>
-      </c>
-      <c r="H84">
-        <v>95.64603501525458</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8">
-      <c r="A85" t="s">
-        <v>10</v>
-      </c>
-      <c r="B85" t="s">
-        <v>17</v>
-      </c>
-      <c r="C85" t="s">
-        <v>23</v>
-      </c>
-      <c r="D85" t="s">
-        <v>29</v>
-      </c>
-      <c r="E85" t="s">
-        <v>32</v>
-      </c>
-      <c r="F85">
-        <v>82215590.80432028</v>
-      </c>
-      <c r="G85">
-        <v>1877045.650711681</v>
-      </c>
-      <c r="H85">
-        <v>43.80052811882774</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8">
-      <c r="A86" t="s">
-        <v>10</v>
-      </c>
-      <c r="B86" t="s">
-        <v>17</v>
-      </c>
-      <c r="C86" t="s">
-        <v>23</v>
-      </c>
-      <c r="D86" t="s">
-        <v>29</v>
-      </c>
-      <c r="E86" t="s">
-        <v>33</v>
-      </c>
-      <c r="F86">
-        <v>59598417.12537961</v>
-      </c>
-      <c r="G86">
-        <v>1877045.650711681</v>
-      </c>
-      <c r="H86">
-        <v>31.75118149246019</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8">
-      <c r="A87" t="s">
-        <v>10</v>
-      </c>
-      <c r="B87" t="s">
-        <v>17</v>
-      </c>
-      <c r="C87" t="s">
-        <v>23</v>
-      </c>
-      <c r="D87" t="s">
-        <v>29</v>
-      </c>
-      <c r="E87" t="s">
-        <v>34</v>
-      </c>
-      <c r="F87">
-        <v>101770759.1934886</v>
-      </c>
-      <c r="G87">
-        <v>1877045.650711681</v>
-      </c>
-      <c r="H87">
-        <v>54.2185850167801</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8">
-      <c r="A88" t="s">
-        <v>10</v>
-      </c>
-      <c r="B88" t="s">
-        <v>17</v>
-      </c>
-      <c r="C88" t="s">
-        <v>23</v>
-      </c>
-      <c r="D88" t="s">
-        <v>29</v>
-      </c>
-      <c r="E88" t="s">
-        <v>35</v>
-      </c>
-      <c r="F88">
-        <v>125709211.348101</v>
-      </c>
-      <c r="G88">
-        <v>1877045.650711681</v>
-      </c>
-      <c r="H88">
-        <v>66.97184551715</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8">
-      <c r="A89" t="s">
-        <v>10</v>
-      </c>
-      <c r="B89" t="s">
-        <v>17</v>
-      </c>
-      <c r="C89" t="s">
-        <v>23</v>
-      </c>
-      <c r="D89" t="s">
-        <v>29</v>
-      </c>
-      <c r="E89" t="s">
-        <v>36</v>
-      </c>
-      <c r="F89">
-        <v>153560351.5188797</v>
-      </c>
-      <c r="G89">
-        <v>1877045.650711681</v>
-      </c>
-      <c r="H89">
-        <v>81.80959874932046</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8">
-      <c r="A90" t="s">
-        <v>10</v>
-      </c>
-      <c r="B90" t="s">
-        <v>17</v>
-      </c>
-      <c r="C90" t="s">
-        <v>23</v>
-      </c>
-      <c r="D90" t="s">
-        <v>29</v>
-      </c>
-      <c r="E90" t="s">
-        <v>37</v>
-      </c>
-      <c r="F90">
-        <v>244295631.6727538</v>
-      </c>
-      <c r="G90">
-        <v>1877045.650711681</v>
-      </c>
-      <c r="H90">
-        <v>130.1490092050395</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8">
-      <c r="A91" t="s">
-        <v>8</v>
-      </c>
-      <c r="B91" t="s">
-        <v>18</v>
-      </c>
-      <c r="C91" t="s">
-        <v>24</v>
-      </c>
-      <c r="D91" t="s">
-        <v>30</v>
-      </c>
-      <c r="E91" t="s">
-        <v>31</v>
-      </c>
-      <c r="F91">
-        <v>9578605.25866594</v>
-      </c>
-      <c r="G91">
-        <v>581200.5213831302</v>
-      </c>
-      <c r="H91">
-        <v>16.48072378853163</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8">
-      <c r="A92" t="s">
-        <v>9</v>
-      </c>
-      <c r="B92" t="s">
-        <v>18</v>
-      </c>
-      <c r="C92" t="s">
-        <v>24</v>
-      </c>
-      <c r="D92" t="s">
-        <v>30</v>
-      </c>
-      <c r="E92" t="s">
-        <v>32</v>
-      </c>
-      <c r="F92">
-        <v>23460773.36651546</v>
-      </c>
-      <c r="G92">
-        <v>581200.5213831302</v>
-      </c>
-      <c r="H92">
-        <v>40.36605698612235</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8">
-      <c r="A93" t="s">
-        <v>9</v>
-      </c>
-      <c r="B93" t="s">
-        <v>18</v>
-      </c>
-      <c r="C93" t="s">
-        <v>24</v>
-      </c>
-      <c r="D93" t="s">
-        <v>30</v>
-      </c>
-      <c r="E93" t="s">
-        <v>33</v>
-      </c>
-      <c r="F93">
-        <v>23712753.26521241</v>
-      </c>
-      <c r="G93">
-        <v>581200.5213831303</v>
-      </c>
-      <c r="H93">
-        <v>40.7996076961205</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8">
-      <c r="A94" t="s">
-        <v>9</v>
-      </c>
-      <c r="B94" t="s">
-        <v>18</v>
-      </c>
-      <c r="C94" t="s">
-        <v>24</v>
-      </c>
-      <c r="D94" t="s">
-        <v>30</v>
-      </c>
-      <c r="E94" t="s">
-        <v>34</v>
-      </c>
-      <c r="F94">
-        <v>29601621.11947902</v>
-      </c>
-      <c r="G94">
-        <v>581200.5213831303</v>
-      </c>
-      <c r="H94">
-        <v>50.93185575441953</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8">
-      <c r="A95" t="s">
-        <v>9</v>
-      </c>
-      <c r="B95" t="s">
-        <v>18</v>
-      </c>
-      <c r="C95" t="s">
-        <v>24</v>
-      </c>
-      <c r="D95" t="s">
-        <v>30</v>
-      </c>
-      <c r="E95" t="s">
-        <v>35</v>
-      </c>
-      <c r="F95">
-        <v>31914186.55862749</v>
-      </c>
-      <c r="G95">
-        <v>581200.5213831303</v>
-      </c>
-      <c r="H95">
-        <v>54.91080166734657</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8">
-      <c r="A96" t="s">
-        <v>9</v>
-      </c>
-      <c r="B96" t="s">
-        <v>18</v>
-      </c>
-      <c r="C96" t="s">
-        <v>24</v>
-      </c>
-      <c r="D96" t="s">
-        <v>30</v>
-      </c>
-      <c r="E96" t="s">
-        <v>36</v>
-      </c>
-      <c r="F96">
-        <v>39252277.85010482</v>
-      </c>
-      <c r="G96">
-        <v>581200.5213831303</v>
-      </c>
-      <c r="H96">
-        <v>67.53654961749341</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8">
-      <c r="A97" t="s">
-        <v>9</v>
-      </c>
-      <c r="B97" t="s">
-        <v>18</v>
-      </c>
-      <c r="C97" t="s">
-        <v>24</v>
-      </c>
-      <c r="D97" t="s">
-        <v>30</v>
-      </c>
-      <c r="E97" t="s">
-        <v>37</v>
-      </c>
-      <c r="F97">
-        <v>47617494.16619965</v>
-      </c>
-      <c r="G97">
-        <v>581200.5213831303</v>
-      </c>
-      <c r="H97">
-        <v>81.92954482022903</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8">
-      <c r="A98" t="s">
-        <v>10</v>
-      </c>
-      <c r="B98" t="s">
-        <v>18</v>
-      </c>
-      <c r="C98" t="s">
-        <v>24</v>
-      </c>
-      <c r="D98" t="s">
-        <v>30</v>
-      </c>
-      <c r="E98" t="s">
-        <v>32</v>
-      </c>
-      <c r="F98">
-        <v>23901795.38850493</v>
-      </c>
-      <c r="G98">
-        <v>581200.5213831302</v>
-      </c>
-      <c r="H98">
-        <v>41.1248691443426</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8">
-      <c r="A99" t="s">
-        <v>10</v>
-      </c>
-      <c r="B99" t="s">
-        <v>18</v>
-      </c>
-      <c r="C99" t="s">
-        <v>24</v>
-      </c>
-      <c r="D99" t="s">
-        <v>30</v>
-      </c>
-      <c r="E99" t="s">
-        <v>33</v>
-      </c>
-      <c r="F99">
-        <v>24687057.98400826</v>
-      </c>
-      <c r="G99">
-        <v>581200.5213831303</v>
-      </c>
-      <c r="H99">
-        <v>42.47597356805265</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8">
-      <c r="A100" t="s">
-        <v>10</v>
-      </c>
-      <c r="B100" t="s">
-        <v>18</v>
-      </c>
-      <c r="C100" t="s">
-        <v>24</v>
-      </c>
-      <c r="D100" t="s">
-        <v>30</v>
-      </c>
-      <c r="E100" t="s">
-        <v>34</v>
-      </c>
-      <c r="F100">
-        <v>31124924.16570021</v>
-      </c>
-      <c r="G100">
-        <v>581200.5213831303</v>
-      </c>
-      <c r="H100">
-        <v>53.55281528590113</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8">
-      <c r="A101" t="s">
-        <v>10</v>
-      </c>
-      <c r="B101" t="s">
-        <v>18</v>
-      </c>
-      <c r="C101" t="s">
-        <v>24</v>
-      </c>
-      <c r="D101" t="s">
-        <v>30</v>
-      </c>
-      <c r="E101" t="s">
-        <v>35</v>
-      </c>
-      <c r="F101">
-        <v>34558762.78802476</v>
-      </c>
-      <c r="G101">
-        <v>581200.5213831303</v>
-      </c>
-      <c r="H101">
-        <v>59.46099756721217</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8">
-      <c r="A102" t="s">
-        <v>10</v>
-      </c>
-      <c r="B102" t="s">
-        <v>18</v>
-      </c>
-      <c r="C102" t="s">
-        <v>24</v>
-      </c>
-      <c r="D102" t="s">
-        <v>30</v>
-      </c>
-      <c r="E102" t="s">
-        <v>36</v>
-      </c>
-      <c r="F102">
-        <v>44641867.37223864</v>
-      </c>
-      <c r="G102">
-        <v>581200.5213831303</v>
-      </c>
-      <c r="H102">
-        <v>76.80975107524121</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8">
-      <c r="A103" t="s">
-        <v>10</v>
-      </c>
-      <c r="B103" t="s">
-        <v>18</v>
-      </c>
-      <c r="C103" t="s">
-        <v>24</v>
-      </c>
-      <c r="D103" t="s">
-        <v>30</v>
-      </c>
-      <c r="E103" t="s">
-        <v>37</v>
-      </c>
-      <c r="F103">
-        <v>55642810.96332396</v>
-      </c>
-      <c r="G103">
-        <v>581200.5213831303</v>
-      </c>
-      <c r="H103">
-        <v>95.73771687421446</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8">
-      <c r="A104" t="s">
-        <v>11</v>
-      </c>
-      <c r="B104" t="s">
-        <v>18</v>
-      </c>
-      <c r="C104" t="s">
-        <v>24</v>
-      </c>
-      <c r="D104" t="s">
-        <v>30</v>
-      </c>
-      <c r="E104" t="s">
-        <v>32</v>
-      </c>
-      <c r="F104">
-        <v>4019737.293083158</v>
-      </c>
-      <c r="G104">
-        <v>581200.5213831302</v>
-      </c>
-      <c r="H104">
-        <v>6.916265807052379</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8">
-      <c r="A105" t="s">
-        <v>11</v>
-      </c>
-      <c r="B105" t="s">
-        <v>18</v>
-      </c>
-      <c r="C105" t="s">
-        <v>24</v>
-      </c>
-      <c r="D105" t="s">
-        <v>30</v>
-      </c>
-      <c r="E105" t="s">
-        <v>33</v>
-      </c>
-      <c r="F105">
-        <v>3310455.780870662</v>
-      </c>
-      <c r="G105">
-        <v>581200.5213831303</v>
-      </c>
-      <c r="H105">
-        <v>5.695892655072814</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8">
-      <c r="A106" t="s">
-        <v>11</v>
-      </c>
-      <c r="B106" t="s">
-        <v>18</v>
-      </c>
-      <c r="C106" t="s">
-        <v>24</v>
-      </c>
-      <c r="D106" t="s">
-        <v>30</v>
-      </c>
-      <c r="E106" t="s">
-        <v>34</v>
-      </c>
-      <c r="F106">
-        <v>4702318.727527466</v>
-      </c>
-      <c r="G106">
-        <v>581200.5213831303</v>
-      </c>
-      <c r="H106">
-        <v>8.090699430786769</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8">
-      <c r="A107" t="s">
-        <v>11</v>
-      </c>
-      <c r="B107" t="s">
-        <v>18</v>
-      </c>
-      <c r="C107" t="s">
-        <v>24</v>
-      </c>
-      <c r="D107" t="s">
-        <v>30</v>
-      </c>
-      <c r="E107" t="s">
-        <v>35</v>
-      </c>
-      <c r="F107">
-        <v>4885823.676316657</v>
-      </c>
-      <c r="G107">
-        <v>581200.5213831303</v>
-      </c>
-      <c r="H107">
-        <v>8.406433746290288</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8">
-      <c r="A108" t="s">
-        <v>11</v>
-      </c>
-      <c r="B108" t="s">
-        <v>18</v>
-      </c>
-      <c r="C108" t="s">
-        <v>24</v>
-      </c>
-      <c r="D108" t="s">
-        <v>30</v>
-      </c>
-      <c r="E108" t="s">
-        <v>36</v>
-      </c>
-      <c r="F108">
-        <v>6280542.93739988</v>
-      </c>
-      <c r="G108">
-        <v>581200.5213831303</v>
-      </c>
-      <c r="H108">
-        <v>10.80615502968504</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8">
-      <c r="A109" t="s">
-        <v>11</v>
-      </c>
-      <c r="B109" t="s">
-        <v>18</v>
-      </c>
-      <c r="C109" t="s">
-        <v>24</v>
-      </c>
-      <c r="D109" t="s">
-        <v>30</v>
-      </c>
-      <c r="E109" t="s">
-        <v>37</v>
-      </c>
-      <c r="F109">
-        <v>7185428.649122512</v>
-      </c>
-      <c r="G109">
-        <v>581200.5213831303</v>
-      </c>
-      <c r="H109">
-        <v>12.36308018448222</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8">
-      <c r="A110" t="s">
-        <v>12</v>
-      </c>
-      <c r="B110" t="s">
-        <v>18</v>
-      </c>
-      <c r="C110" t="s">
-        <v>24</v>
-      </c>
-      <c r="D110" t="s">
-        <v>30</v>
-      </c>
-      <c r="E110" t="s">
-        <v>32</v>
-      </c>
-      <c r="F110">
-        <v>3873813.459940849</v>
-      </c>
-      <c r="G110">
-        <v>581200.5213831303</v>
-      </c>
-      <c r="H110">
-        <v>6.665192678633562</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8">
-      <c r="A111" t="s">
-        <v>12</v>
-      </c>
-      <c r="B111" t="s">
-        <v>18</v>
-      </c>
-      <c r="C111" t="s">
-        <v>24</v>
-      </c>
-      <c r="D111" t="s">
-        <v>30</v>
-      </c>
-      <c r="E111" t="s">
-        <v>33</v>
-      </c>
-      <c r="F111">
-        <v>3726355.309924745</v>
-      </c>
-      <c r="G111">
-        <v>581200.5213831303</v>
-      </c>
-      <c r="H111">
-        <v>6.411479640549586</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8">
-      <c r="A112" t="s">
-        <v>12</v>
-      </c>
-      <c r="B112" t="s">
-        <v>18</v>
-      </c>
-      <c r="C112" t="s">
-        <v>24</v>
-      </c>
-      <c r="D112" t="s">
-        <v>30</v>
-      </c>
-      <c r="E112" t="s">
-        <v>34</v>
-      </c>
-      <c r="F112">
-        <v>5207537.167814495</v>
-      </c>
-      <c r="G112">
-        <v>581200.5213831303</v>
-      </c>
-      <c r="H112">
-        <v>8.959966442255926</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8">
-      <c r="A113" t="s">
-        <v>12</v>
-      </c>
-      <c r="B113" t="s">
-        <v>18</v>
-      </c>
-      <c r="C113" t="s">
-        <v>24</v>
-      </c>
-      <c r="D113" t="s">
-        <v>30</v>
-      </c>
-      <c r="E113" t="s">
-        <v>35</v>
-      </c>
-      <c r="F113">
-        <v>5107268.991712712</v>
-      </c>
-      <c r="G113">
-        <v>581200.5213831303</v>
-      </c>
-      <c r="H113">
-        <v>8.787447367663274</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8">
-      <c r="A114" t="s">
-        <v>12</v>
-      </c>
-      <c r="B114" t="s">
-        <v>18</v>
-      </c>
-      <c r="C114" t="s">
-        <v>24</v>
-      </c>
-      <c r="D114" t="s">
-        <v>30</v>
-      </c>
-      <c r="E114" t="s">
-        <v>36</v>
-      </c>
-      <c r="F114">
-        <v>7737317.911446427</v>
-      </c>
-      <c r="G114">
-        <v>581200.5213831303</v>
-      </c>
-      <c r="H114">
-        <v>13.31264791888572</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8">
-      <c r="A115" t="s">
-        <v>12</v>
-      </c>
-      <c r="B115" t="s">
-        <v>18</v>
-      </c>
-      <c r="C115" t="s">
-        <v>24</v>
-      </c>
-      <c r="D115" t="s">
-        <v>30</v>
-      </c>
-      <c r="E115" t="s">
-        <v>37</v>
-      </c>
-      <c r="F115">
-        <v>9198722.426902626</v>
-      </c>
-      <c r="G115">
-        <v>581200.5213831303</v>
-      </c>
-      <c r="H115">
-        <v>15.82710628856918</v>
+        <v>97.64561693799659</v>
       </c>
     </row>
   </sheetData>

--- a/results/per_capita_hours/per_capita_hours_summary.xlsx
+++ b/results/per_capita_hours/per_capita_hours_summary.xlsx
@@ -863,13 +863,13 @@
         <v>29</v>
       </c>
       <c r="F15">
-        <v>48270164.89642763</v>
+        <v>2998794.413036864</v>
       </c>
       <c r="G15">
         <v>4875767.960493487</v>
       </c>
       <c r="H15">
-        <v>9.900012733900098</v>
+        <v>0.6150404279561633</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -889,13 +889,13 @@
         <v>30</v>
       </c>
       <c r="F16">
-        <v>251202904.7250491</v>
+        <v>23464606.0475476</v>
       </c>
       <c r="G16">
         <v>4875767.960493487</v>
       </c>
       <c r="H16">
-        <v>51.52068489732319</v>
+        <v>4.812494408608545</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -915,13 +915,13 @@
         <v>31</v>
       </c>
       <c r="F17">
-        <v>124441206.1083353</v>
+        <v>7777400.633292485</v>
       </c>
       <c r="G17">
-        <v>4875767.960493487</v>
+        <v>4875767.960493488</v>
       </c>
       <c r="H17">
-        <v>25.5223807032319</v>
+        <v>1.595112953756174</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -941,13 +941,13 @@
         <v>32</v>
       </c>
       <c r="F18">
-        <v>167219007.2268224</v>
+        <v>11503842.52458295</v>
       </c>
       <c r="G18">
         <v>4875767.960493487</v>
       </c>
       <c r="H18">
-        <v>34.29593216529891</v>
+        <v>2.359390893453966</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -967,13 +967,13 @@
         <v>33</v>
       </c>
       <c r="F19">
-        <v>301335204.3163406</v>
+        <v>20292248.27595226</v>
       </c>
       <c r="G19">
         <v>4875767.960493487</v>
       </c>
       <c r="H19">
-        <v>61.80261381549457</v>
+        <v>4.161856848064286</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -993,13 +993,13 @@
         <v>34</v>
       </c>
       <c r="F20">
-        <v>338011099.3954629</v>
+        <v>24285808.9454489</v>
       </c>
       <c r="G20">
         <v>4875767.960493487</v>
       </c>
       <c r="H20">
-        <v>69.32468938928999</v>
+        <v>4.980919752996383</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1019,13 +1019,13 @@
         <v>35</v>
       </c>
       <c r="F21">
-        <v>548669598.3561199</v>
+        <v>53930545.65671132</v>
       </c>
       <c r="G21">
         <v>4875767.960493487</v>
       </c>
       <c r="H21">
-        <v>112.5298830464828</v>
+        <v>11.0609335993202</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1045,13 +1045,13 @@
         <v>30</v>
       </c>
       <c r="F22">
-        <v>284476637.2697743</v>
+        <v>40310402.00014576</v>
       </c>
       <c r="G22">
         <v>4875767.960493487</v>
       </c>
       <c r="H22">
-        <v>58.34499089677388</v>
+        <v>8.267498028365125</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1071,13 +1071,13 @@
         <v>31</v>
       </c>
       <c r="F23">
-        <v>131137651.5815994</v>
+        <v>8645243.412704293</v>
       </c>
       <c r="G23">
         <v>4875767.960493487</v>
       </c>
       <c r="H23">
-        <v>26.89579418958375</v>
+        <v>1.773103946445657</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1097,13 +1097,13 @@
         <v>32</v>
       </c>
       <c r="F24">
-        <v>179777609.077431</v>
+        <v>11227412.73046915</v>
       </c>
       <c r="G24">
         <v>4875767.960493487</v>
       </c>
       <c r="H24">
-        <v>36.87164986810309</v>
+        <v>2.302696277066638</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1123,13 +1123,13 @@
         <v>33</v>
       </c>
       <c r="F25">
-        <v>371871351.1063213</v>
+        <v>30463632.50179698</v>
       </c>
       <c r="G25">
         <v>4875767.960493487</v>
       </c>
       <c r="H25">
-        <v>76.26928806281491</v>
+        <v>6.247966012458412</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1149,13 +1149,13 @@
         <v>34</v>
       </c>
       <c r="F26">
-        <v>437714015.6131574</v>
+        <v>36508304.11408615</v>
       </c>
       <c r="G26">
         <v>4875767.960493487</v>
       </c>
       <c r="H26">
-        <v>89.77334835451344</v>
+        <v>7.487703354609817</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1175,13 +1175,13 @@
         <v>35</v>
       </c>
       <c r="F27">
-        <v>699174128.6019485</v>
+        <v>116031967.5918008</v>
       </c>
       <c r="G27">
         <v>4875767.960493487</v>
       </c>
       <c r="H27">
-        <v>143.3977445742073</v>
+        <v>23.79768039249698</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1201,13 +1201,13 @@
         <v>29</v>
       </c>
       <c r="F28">
-        <v>25167587.86489875</v>
+        <v>3773239.618111828</v>
       </c>
       <c r="G28">
-        <v>1488498.682202911</v>
+        <v>1488498.682202912</v>
       </c>
       <c r="H28">
-        <v>16.90803503275653</v>
+        <v>2.534929767305942</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1227,13 +1227,13 @@
         <v>30</v>
       </c>
       <c r="F29">
-        <v>74022142.65882272</v>
+        <v>16337453.69205924</v>
       </c>
       <c r="G29">
         <v>1488498.682202911</v>
       </c>
       <c r="H29">
-        <v>49.72939750895396</v>
+        <v>10.97579318503698</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1253,13 +1253,13 @@
         <v>31</v>
       </c>
       <c r="F30">
-        <v>57181720.09318546</v>
+        <v>9485595.328886777</v>
       </c>
       <c r="G30">
         <v>1488498.682202911</v>
       </c>
       <c r="H30">
-        <v>38.41570085138341</v>
+        <v>6.372592359200829</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1279,13 +1279,13 @@
         <v>32</v>
       </c>
       <c r="F31">
-        <v>59436313.39123303</v>
+        <v>10661977.06483491</v>
       </c>
       <c r="G31">
-        <v>1488498.682202911</v>
+        <v>1488498.682202912</v>
       </c>
       <c r="H31">
-        <v>39.9303768971229</v>
+        <v>7.16290662014941</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1305,13 +1305,13 @@
         <v>33</v>
       </c>
       <c r="F32">
-        <v>79530650.97178617</v>
+        <v>14742087.31239488</v>
       </c>
       <c r="G32">
         <v>1488498.682202911</v>
       </c>
       <c r="H32">
-        <v>53.43011177818738</v>
+        <v>9.903997557174353</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1331,13 +1331,13 @@
         <v>34</v>
       </c>
       <c r="F33">
-        <v>93782960.82160889</v>
+        <v>21819105.7242656</v>
       </c>
       <c r="G33">
-        <v>1488498.682202911</v>
+        <v>1488498.682202912</v>
       </c>
       <c r="H33">
-        <v>63.00506808834677</v>
+        <v>14.6584649251918</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1357,13 +1357,13 @@
         <v>35</v>
       </c>
       <c r="F34">
-        <v>105205951.7959697</v>
+        <v>15516009.14979264</v>
       </c>
       <c r="G34">
         <v>1488498.682202911</v>
       </c>
       <c r="H34">
-        <v>70.67923744498694</v>
+        <v>10.42393207015114</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1383,13 +1383,13 @@
         <v>30</v>
       </c>
       <c r="F35">
-        <v>79922569.19465432</v>
+        <v>17664110.97627698</v>
       </c>
       <c r="G35">
         <v>1488498.682202911</v>
       </c>
       <c r="H35">
-        <v>53.6934094401565</v>
+        <v>11.86706524330602</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1409,13 +1409,13 @@
         <v>31</v>
       </c>
       <c r="F36">
-        <v>61766266.52293781</v>
+        <v>10219836.09051061</v>
       </c>
       <c r="G36">
         <v>1488498.682202911</v>
       </c>
       <c r="H36">
-        <v>41.49568102507588</v>
+        <v>6.865868416749764</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1435,13 +1435,13 @@
         <v>32</v>
       </c>
       <c r="F37">
-        <v>62213081.00389005</v>
+        <v>11312415.87762689</v>
       </c>
       <c r="G37">
         <v>1488498.682202911</v>
       </c>
       <c r="H37">
-        <v>41.79585897369924</v>
+        <v>7.59988303173035</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1461,13 +1461,13 @@
         <v>33</v>
       </c>
       <c r="F38">
-        <v>83717361.68954626</v>
+        <v>14358190.91688073</v>
       </c>
       <c r="G38">
         <v>1488498.682202911</v>
       </c>
       <c r="H38">
-        <v>56.24281881502797</v>
+        <v>9.646089102095308</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1487,13 +1487,13 @@
         <v>34</v>
       </c>
       <c r="F39">
-        <v>102845171.9042636</v>
+        <v>24684482.57113159</v>
       </c>
       <c r="G39">
-        <v>1488498.682202911</v>
+        <v>1488498.682202912</v>
       </c>
       <c r="H39">
-        <v>69.09322334908441</v>
+        <v>16.58347626791289</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1513,13 +1513,13 @@
         <v>35</v>
       </c>
       <c r="F40">
-        <v>126129203.164016</v>
+        <v>17952993.38865525</v>
       </c>
       <c r="G40">
-        <v>1488498.682202911</v>
+        <v>1488498.682202912</v>
       </c>
       <c r="H40">
-        <v>84.73585141328472</v>
+        <v>12.06114160751934</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -2215,13 +2215,13 @@
         <v>29</v>
       </c>
       <c r="F67">
-        <v>9611853.890797934</v>
+        <v>1502032.577106653</v>
       </c>
       <c r="G67">
         <v>581200.5213831303</v>
       </c>
       <c r="H67">
-        <v>16.53793060598745</v>
+        <v>2.584362060674247</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -2241,13 +2241,13 @@
         <v>30</v>
       </c>
       <c r="F68">
-        <v>23537614.43377975</v>
+        <v>4023973.716483801</v>
       </c>
       <c r="G68">
-        <v>581200.5213831302</v>
+        <v>581200.5213831303</v>
       </c>
       <c r="H68">
-        <v>40.49826792612878</v>
+        <v>6.923554897899303</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -2267,13 +2267,13 @@
         <v>31</v>
       </c>
       <c r="F69">
-        <v>24043301.39199234</v>
+        <v>3369503.837609507</v>
       </c>
       <c r="G69">
         <v>581200.5213831303</v>
       </c>
       <c r="H69">
-        <v>41.36834105856364</v>
+        <v>5.797489358046039</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -2293,13 +2293,13 @@
         <v>32</v>
       </c>
       <c r="F70">
-        <v>29705670.82749488</v>
+        <v>4704354.536801483</v>
       </c>
       <c r="G70">
         <v>581200.5213831303</v>
       </c>
       <c r="H70">
-        <v>51.11088124422509</v>
+        <v>8.09420219652616</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -2319,13 +2319,13 @@
         <v>33</v>
       </c>
       <c r="F71">
-        <v>32301700.19586874</v>
+        <v>4917846.582171896</v>
       </c>
       <c r="G71">
         <v>581200.5213831303</v>
       </c>
       <c r="H71">
-        <v>55.57754855243031</v>
+        <v>8.461531607832173</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -2345,13 +2345,13 @@
         <v>34</v>
       </c>
       <c r="F72">
-        <v>39875542.95589899</v>
+        <v>6366657.968148972</v>
       </c>
       <c r="G72">
         <v>581200.5213831303</v>
       </c>
       <c r="H72">
-        <v>68.60892495588942</v>
+        <v>10.95432253398141</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -2371,13 +2371,13 @@
         <v>35</v>
       </c>
       <c r="F73">
-        <v>48634074.77448445</v>
+        <v>7388690.159301756</v>
       </c>
       <c r="G73">
         <v>581200.5213831303</v>
       </c>
       <c r="H73">
-        <v>83.6786495971235</v>
+        <v>12.71280717663206</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -2397,13 +2397,13 @@
         <v>30</v>
       </c>
       <c r="F74">
-        <v>24058847.09306264</v>
+        <v>3886765.439179313</v>
       </c>
       <c r="G74">
-        <v>581200.5213831302</v>
+        <v>581200.5213831303</v>
       </c>
       <c r="H74">
-        <v>41.3950886276011</v>
+        <v>6.687477550656115</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -2423,13 +2423,13 @@
         <v>31</v>
       </c>
       <c r="F75">
-        <v>25130380.62437433</v>
+        <v>3771226.430901154</v>
       </c>
       <c r="G75">
         <v>581200.5213831303</v>
       </c>
       <c r="H75">
-        <v>43.23874411634992</v>
+        <v>6.488683840004923</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -2449,13 +2449,13 @@
         <v>32</v>
       </c>
       <c r="F76">
-        <v>31292978.57426723</v>
+        <v>5196531.633656358</v>
       </c>
       <c r="G76">
         <v>581200.5213831303</v>
       </c>
       <c r="H76">
-        <v>53.84196576389294</v>
+        <v>8.941030578034837</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -2475,13 +2475,13 @@
         <v>33</v>
       </c>
       <c r="F77">
-        <v>34841162.98658558</v>
+        <v>5120402.503682895</v>
       </c>
       <c r="G77">
         <v>581200.5213831303</v>
       </c>
       <c r="H77">
-        <v>59.94688873243131</v>
+        <v>8.810044580650848</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -2501,13 +2501,13 @@
         <v>34</v>
       </c>
       <c r="F78">
-        <v>45364412.37610775</v>
+        <v>7791663.794065985</v>
       </c>
       <c r="G78">
         <v>581200.5213831303</v>
       </c>
       <c r="H78">
-        <v>78.05294508021149</v>
+        <v>13.40615417123771</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -2527,13 +2527,13 @@
         <v>35</v>
       </c>
       <c r="F79">
-        <v>56751683.47514104</v>
+        <v>9270144.197026446</v>
       </c>
       <c r="G79">
         <v>581200.5213831303</v>
       </c>
       <c r="H79">
-        <v>97.64561693799659</v>
+        <v>15.94999291288578</v>
       </c>
     </row>
   </sheetData>
